--- a/literature-management.xlsx
+++ b/literature-management.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jay/phd/papers/sok - a survey on software power monitoring tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702037E0-4BD6-9B4E-B3E1-4CD7B809AED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE64065-D85E-B646-827F-AA68693ADDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10280" yWindow="-28140" windowWidth="50880" windowHeight="27980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29920" windowHeight="18560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tools" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="186">
   <si>
     <t>Year</t>
   </si>
@@ -135,9 +135,6 @@
     <t>Kepler is a tool to collect fine‑grained energy and power metrics (e.g., CPU energy, memory, power usage) by monitoring containers, pods, and nodes in Kubernetes via eBPF, RAPL, cgroups and exporting them as Prometheus metrics, with support for multiple metric sources and attribution to workloads.</t>
   </si>
   <si>
-    <t>Prometheus</t>
-  </si>
-  <si>
     <t>websitecarbon.com</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
   </si>
   <si>
     <t>PETRA</t>
-  </si>
-  <si>
-    <t>PowerAPI</t>
   </si>
   <si>
     <t>PowerJoular</t>
@@ -369,9 +363,6 @@
     <t>yes ((To be discussed : need to dive in a bit more)</t>
   </si>
   <si>
-    <t>~ms</t>
-  </si>
-  <si>
     <t>Case Studies</t>
   </si>
   <si>
@@ -397,15 +388,6 @@
   </si>
   <si>
     <t>no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target device is a smartphone. The authors use supervised learning to  train models (linear, nn, random forest, …) to estimate (i) system-level energy (ii) component-level shares of enregy i.e. CPU, display, WIFi, Memory,… Both based on component-related metrics (e.g. display brightness, CPU frequency,...)
-. The framework involves the creation of a dataset: create scenarios putting the device under a random workload. Then collect features i.e. component-related metrics, and ODPM power rails values as target variables. 
-The study shows Gradient boosting trees estimate best (i).
-Linear regression is used to estimate (ii):
-CPU/Memory, GPU, Display energy consumption are successfully estimated while CPU/Memory block has highest accuracy (absolute error ~7%)
- Under that case study, the authors show they need at least 500 runs (capping the dataset size) to have a stable R-squared 
-</t>
   </si>
   <si>
     <t>No software-level attribution</t>
@@ -467,13 +449,7 @@
     <t>https://aknostic.com/keit/</t>
   </si>
   <si>
-    <t>Not really software based</t>
-  </si>
-  <si>
     <t>???</t>
-  </si>
-  <si>
-    <t>Needs wrapper for this</t>
   </si>
   <si>
     <t>Allows periodic checks of
@@ -521,25 +497,12 @@
 (1ms for RAPL metric provider)</t>
   </si>
   <si>
-    <t>may include 
-embedded GPU chipset
-on some system</t>
-  </si>
-  <si>
     <t>~ms at RAPL read level
 Effective resolution = Prometheus scrape interval
 (typically 1s–30s depending on configuration)</t>
   </si>
   <si>
     <t>✗ (RAPL, NVLM, IPMI)</t>
-  </si>
-  <si>
-    <t>no (But investigate what is Psys domain in RAPL:
-Some doc says the
-psys domain could be 
-used to report connected 
-peripherals : "https://hubblo-org.github.io/scaphandre-documentation/explanations/rapl-domains.html"
-while this  paper says it's more a system level metric : "(Raffin and Trystram 2024)")</t>
   </si>
   <si>
     <t>Modeled and allocated
@@ -612,28 +575,106 @@
     <t>Active (Last Commit in March 2026)</t>
   </si>
   <si>
-    <t>System-Level</t>
-  </si>
-  <si>
     <t>Class Level
  Method Level</t>
   </si>
   <si>
-    <t>https://www.green-coding.io/case-studies/rapl-and-sgx/</t>
-  </si>
-  <si>
-    <t>Need to be handled in a wrapper</t>
-  </si>
-  <si>
-    <t>RAPL
-Does it fit in this table? Definitely used as a primitive by other tools but only reports system-level metrics</t>
+    <t>✗ (Linux System/Windows)</t>
+  </si>
+  <si>
+    <t>Support for VM "exposing System-level metrics from host to VM"</t>
+  </si>
+  <si>
+    <t>no : "No, until your cloud provider uses scaphandre on its hypervisors"</t>
+  </si>
+  <si>
+    <t>SoftWatt</t>
+  </si>
+  <si>
+    <t>from Li, Tao, and Lizy Kurian John. 2003. ‘Run-Time Modeling and Estimation of Operating System Power Consumption’. Proceedings of the 2003 ACM SIGMETRICS International Conference on Measurement and Modeling of Computer Systems (New York, NY, USA), SIGMETRICS ’03, 160–71. https://doi.org/10.1145/781027.781048.</t>
+  </si>
+  <si>
+    <t>PowerScope</t>
+  </si>
+  <si>
+    <t>from Noureddine, Adel, Romain Rouvoy, and Lionel Seinturier. 2013. ‘A Review of Energy Measurement Approaches’. SIGOPS Oper. Syst. Rev. 47 (3): 42–49. https://doi.org/10.1145/2553070.2553077.</t>
+  </si>
+  <si>
+    <t>pTop</t>
+  </si>
+  <si>
+    <t>PowerTop</t>
+  </si>
+  <si>
+    <t>Energy Checker</t>
+  </si>
+  <si>
+    <t>Joulemeter</t>
+  </si>
+  <si>
+    <t>from Wysocki, Włodzimierz, Ireneusz Miciuła, and Przemysław Plecka. 2025. ‘Methods of Improving Software Energy Efficiency: A Systematic Literature Review and the Current State of Applied Methods in Practice’. Electronics 14 (7): 1331. https://doi.org/10.3390/electronics14071331.</t>
+  </si>
+  <si>
+    <t>Hubblo-org</t>
+  </si>
+  <si>
+    <t>Scaphandre is an open-source energy monitoring agent developed by Hubblo. It uses Intel RAPL to measure CPU (and optionally DRAM) energy at the system level and attributes it to processes or containers based on CPU usage. It runs as a lightweight daemon and exports metrics to Prometheus, enabling integration in cloud and container environments. Accuracy is high at system level but limited for fine-grained attribution.</t>
+  </si>
+  <si>
+    <t>Stress Terminal UI (s-tui) is an open-source monitoring tool that provides real-time visualisation of system performance and power-related metrics. It reads data from hardware interfaces such as Intel RAPL and system sensors to display CPU usage, frequency, temperature, and estimated power consumption. Designed as a terminal-based interface, it is mainly used for local monitoring and stress testing on Linux systems rather than fine-grained software energy attribution.</t>
+  </si>
+  <si>
+    <t>Alex Manos</t>
+  </si>
+  <si>
+    <t>(Wysocki et al. 2025)</t>
+  </si>
+  <si>
+    <t>Kenan Liu</t>
+  </si>
+  <si>
+    <t>Target device is a smartphone. The authors use supervised learning to  train models (linear, nn, random forest, …) to estimate (i) system-level energy (ii) component-level shares of enregy i.e. CPU, display, WIFi, Memory,… Both based on component-related metrics (e.g. display brightness, CPU frequency,...)
+. The framework involves the creation of a dataset: create scenarios putting the device under a random workload. Then collect features i.e. component-related metrics, and ODPM power rails values as target variables. 
+The study shows Gradient boosting trees estimate best (i).
+Linear regression is used to estimate (ii):
+CPU/Memory, GPU, Display energy consumption are successfully estimated while CPU/Memory block has highest accuracy (absolute error ~7%)
+ Under that case study, the authors show they need at least 500 runs (capping the dataset size) to have a stable R-squared</t>
+  </si>
+  <si>
+    <t>jRAPL is a Java library that allows to profile the energy consumption of parts of program code by relying on RAPL. 
+To use it, the developer just needs to put API calls (statCheck) before and after a code block. The energy consumption is then computed as the difference between the two readings. It can also report time metrics (wall-clock, user, kernel time) and some low-level counters, which can be useful for analysis.
+It allows a fine-grained attribution, both in terms of hardware components (RAPL usual granularity) and program structure (methods, code blocks…). Also, since the measurement is directly embedded in the code, there is no need to synchronise measurement and execution, which is usually a pain with external setups.
+It is not completely free: accessing MSRs introduces a small overhead (microseconds), even if in practice it remains quite low compared to execution time.
+Overall, jRAPL can be seen as a hardware-based energy metering approach, with relatively low overhead and good granularity, but at the cost of some code instrumentation. (Liu et al. 2015)</t>
+  </si>
+  <si>
+    <t>e-Surgeon (= Jalen + PowerAPI)</t>
+  </si>
+  <si>
+    <t>CERN (Khan et al. 2015)</t>
+  </si>
+  <si>
+    <t>IgProf is originally an application profiler developed at CERN to analyse performance and memory behaviour of programs, and was later extended with an energy profiling module. This module enables the attribution of energy consumption within a program, typically at the level of functions.
+The approach relies on statistical sampling. At regular intervals, the profiler reads energy values from RAPL (through the PAPI library) and attributes the energy difference to the current execution point. This allows building energy profiles in the same way as traditional performance profiles (e.g., flat profiles (cumulated energy offunction and called sub-function) or call graphs)
+One advantage is that IgProf operates entirely in user space and does not require recompilation of the application. This makes it relatively non-intrusive compared to instrumentation-based approaches. It can also handle dynamically loaded libraries, which is useful in complex software stacks.
+In terms of granularity, the tool provides fine-grained attribution at function level, but this is based on sampling and indirect attribution rather than exact measurement. As a result, short-lived code sections (shorter than the RAPL update interval, ~1 ms) may not be measured accurately, and multi-threaded scenarios introduce additional challenges in attributing energy correctly. (Khan et al. 2015)   
+Overall, IgProf can be seen as a sampling-based, hardware-informed energy profiling approach. It offers good integration with performance profiling and low intrusiveness, but with limitations in accuracy for short events and complex concurrent workloads.</t>
+  </si>
+  <si>
+    <t>Khan, Kashif, Filip Nybäck, Zhonghong Ou, et al. 2015. Energy Profiling Using IgProf. In Proceedings - 2015 IEEE/ACM 15th International Symposium on Cluster, Cloud, and Grid Computing, CCGrid 2015. https://doi.org/10.1109/CCGrid.2015.118.</t>
+  </si>
+  <si>
+    <t>Liu, Kenan, Gustavo Pinto, and Yu David Liu. 2015. ‘Data-Oriented Characterization of Application-Level Energy Optimization’. In Fundamental Approaches to Software Engineering, edited by Alexander Egyed and Ina Schaefer. Springer. https://doi.org/10.1007/978-3-662-46675-9_21.</t>
+  </si>
+  <si>
+    <t>Noureddine, Adel. (2021) 2022. ‘PowerJoular and JoularJX: Multi-Platform Software Power Monitoring Tools’. In Proceedings of the 18th International Conference on Intelligent Environments, Ada. Intelligent Environments. March 22; IEEE, released. https://doi.org/10.1109/IE54923.2022.9826760.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,8 +730,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -791,6 +839,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -924,7 +978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -986,17 +1040,8 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1177,15 +1222,40 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1207,6 +1277,25 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1226,25 +1315,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="3" tint="0.39997558519241921"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1418,13 +1488,13 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{DF00C389-F294-FB48-80B0-022781D38C47}">
-      <tableStyleElement type="wholeTable" dxfId="18"/>
+      <tableStyleElement type="wholeTable" dxfId="19"/>
     </tableStyle>
     <tableStyle name="Table Style 2" pivot="0" count="4" xr9:uid="{66177898-DED3-9C47-8DA6-ABD521A19111}">
-      <tableStyleElement type="wholeTable" dxfId="17"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="secondRowStripe" dxfId="14"/>
+      <tableStyleElement type="wholeTable" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="secondRowStripe" dxfId="15"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1439,18 +1509,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C9355DD-35BE-3D46-8331-B67246AE3C74}" name="Table1" displayName="Table1" ref="C2:K22" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C9355DD-35BE-3D46-8331-B67246AE3C74}" name="Table1" displayName="Table1" ref="C2:K22" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="C2:K22" xr:uid="{1C9355DD-35BE-3D46-8331-B67246AE3C74}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B697189A-DF2B-4341-9FF4-7259FA9252F8}" name="Tool Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{F3B719A6-5185-6144-A373-7DD05C5FE758}" name="References" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{271ED028-8F14-D741-A569-E2FEB926BB1C}" name="Year" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{B7FF3EF8-B658-904B-8045-D98673D5126F}" name="Authors/Institution" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{63D16556-412F-8B4C-BF7C-5FF77216838E}" name="Discovery Method" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{946E4FD2-8FE0-9345-A39D-83A4386577DF}" name="Discovered From" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{DF93B5C3-BD8E-D543-8F4C-AC0C5199BC07}" name="Selection Status" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{03969A93-C0C5-BB4C-ACA8-090EAA97265A}" name="Exclusion Reason" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{01558EB7-81C3-6642-A7E2-29E574F37760}" name="Short Description" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B697189A-DF2B-4341-9FF4-7259FA9252F8}" name="Tool Name" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{F3B719A6-5185-6144-A373-7DD05C5FE758}" name="References" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{271ED028-8F14-D741-A569-E2FEB926BB1C}" name="Year" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{B7FF3EF8-B658-904B-8045-D98673D5126F}" name="Authors/Institution" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{63D16556-412F-8B4C-BF7C-5FF77216838E}" name="Discovery Method" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{946E4FD2-8FE0-9345-A39D-83A4386577DF}" name="Discovered From" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{DF93B5C3-BD8E-D543-8F4C-AC0C5199BC07}" name="Selection Status" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{03969A93-C0C5-BB4C-ACA8-090EAA97265A}" name="Exclusion Reason" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{01558EB7-81C3-6642-A7E2-29E574F37760}" name="Short Description" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1745,56 +1815,56 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="11" customWidth="1"/>
+    <col min="3" max="3" width="28" style="11" customWidth="1"/>
     <col min="4" max="4" width="219.33203125" style="18" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="29" style="13" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="24.33203125" style="11" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" style="11" customWidth="1"/>
-    <col min="10" max="10" width="25" style="11" customWidth="1"/>
-    <col min="11" max="11" width="70.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="82.33203125" style="11" customWidth="1"/>
     <col min="12" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="20" x14ac:dyDescent="0.25">
       <c r="B2"/>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" ht="48" x14ac:dyDescent="0.2">
       <c r="B3"/>
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="28" t="s">
-        <v>53</v>
+      <c r="D3" s="89" t="s">
+        <v>51</v>
       </c>
       <c r="E3" s="8">
         <v>2022</v>
@@ -1815,7 +1885,7 @@
         <v>35</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="80" x14ac:dyDescent="0.2">
@@ -1823,8 +1893,8 @@
       <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>54</v>
+      <c r="D4" s="89" t="s">
+        <v>52</v>
       </c>
       <c r="E4" s="6">
         <v>2023</v>
@@ -1851,22 +1921,22 @@
     <row r="5" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B5"/>
       <c r="C5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>52</v>
+        <v>180</v>
+      </c>
+      <c r="D5" s="89" t="s">
+        <v>50</v>
       </c>
       <c r="E5" s="6">
         <v>2012</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>30</v>
@@ -1875,186 +1945,260 @@
         <v>35</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="64" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="48" x14ac:dyDescent="0.2">
       <c r="B6"/>
       <c r="C6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="90" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="F6" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="32" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B7"/>
       <c r="C7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="21"/>
+      <c r="E7" s="8">
+        <v>2020</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>172</v>
+      </c>
       <c r="G7" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="21"/>
-    </row>
-    <row r="8" spans="2:11" ht="32" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B8"/>
       <c r="C8" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="17"/>
+      <c r="E8" s="6">
+        <v>2017</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>175</v>
+      </c>
       <c r="G8" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" spans="2:11" ht="244" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="272" x14ac:dyDescent="0.2">
       <c r="B9"/>
       <c r="C9" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="D9" s="89" t="s">
+        <v>107</v>
       </c>
       <c r="E9" s="6">
         <v>2025</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="272" x14ac:dyDescent="0.2">
       <c r="B10"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-    </row>
-    <row r="11" spans="2:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="92" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2015</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="335" x14ac:dyDescent="0.2">
       <c r="B11"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="91" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2015</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="32" x14ac:dyDescent="0.2">
       <c r="B12"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="6"/>
+      <c r="C12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2021</v>
+      </c>
       <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="14"/>
+      <c r="G12" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="K12" s="14"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13"/>
-      <c r="D13" s="27"/>
+      <c r="D13" s="91"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="91"/>
       <c r="E14" s="10"/>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
       <c r="H14" s="15"/>
+      <c r="I14" s="7"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
-      <c r="D15" s="27"/>
+      <c r="D15" s="91"/>
       <c r="E15" s="10"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
       <c r="H15" s="15"/>
+      <c r="I15" s="7"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="27"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="10"/>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
       <c r="H16" s="15"/>
+      <c r="I16" s="7"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="27"/>
+      <c r="D17" s="91"/>
       <c r="E17" s="10"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
@@ -2065,7 +2209,7 @@
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="27"/>
+      <c r="D18" s="91"/>
       <c r="E18" s="10"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
@@ -2076,7 +2220,7 @@
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="27"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="10"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
@@ -2087,7 +2231,7 @@
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="27"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="10"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
@@ -2098,8 +2242,8 @@
     <row r="21" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="27" t="s">
-        <v>108</v>
+      <c r="D21" s="91" t="s">
+        <v>105</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="18"/>
@@ -2111,7 +2255,7 @@
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="27"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="10"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
@@ -2122,7 +2266,7 @@
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="27"/>
+      <c r="D23" s="25"/>
       <c r="E23" s="10"/>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
@@ -2133,7 +2277,7 @@
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
-      <c r="D24" s="27"/>
+      <c r="D24" s="25"/>
       <c r="E24" s="10"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
@@ -2143,7 +2287,7 @@
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
-      <c r="D25" s="27"/>
+      <c r="D25" s="25"/>
       <c r="E25" s="10"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
@@ -2152,7 +2296,7 @@
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="25"/>
       <c r="E26" s="10"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
@@ -2161,7 +2305,7 @@
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="27"/>
+      <c r="D27" s="25"/>
       <c r="E27" s="10"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
@@ -2170,176 +2314,201 @@
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="25"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="2:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="10"/>
-      <c r="C29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>133</v>
-      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="25"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
       <c r="H29" s="15"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" ht="32" x14ac:dyDescent="0.2">
       <c r="B30" s="10"/>
       <c r="C30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="27"/>
+        <v>39</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>171</v>
+      </c>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" ht="32" x14ac:dyDescent="0.2">
       <c r="B31" s="10"/>
       <c r="C31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="27"/>
+        <v>40</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>171</v>
+      </c>
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="10"/>
-      <c r="C32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="27"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="25"/>
       <c r="G32" s="18"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="10"/>
-      <c r="C33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="27"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="25"/>
       <c r="G33" s="18"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="B34" s="10"/>
       <c r="C34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="C35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="27"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C35" s="6" t="s">
+      <c r="D35" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="C36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D35" s="27"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C36" s="6" t="s">
+      <c r="D36" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="C37" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="27"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="C38" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="27"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C38" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="27"/>
+      <c r="D38" s="25" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C39" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="27"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C40" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="27"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="25"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D41" s="27"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C42" s="6" t="s">
+      <c r="D41" s="25"/>
+    </row>
+    <row r="42" spans="2:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="C42" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D43" s="25"/>
+    </row>
+    <row r="44" spans="2:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="C44" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="C45" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D46" s="25"/>
+    </row>
+    <row r="47" spans="2:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="C47" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="C48" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="C49" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D50" s="25"/>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D51" s="25"/>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D52" s="25"/>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="27"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D43" s="27"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" s="27"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D45" s="27"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D46" s="27"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C47" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="D47" s="27"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D48" s="27"/>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D49" s="27"/>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D50" s="27"/>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D51" s="27"/>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D52" s="27"/>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D53" s="27"/>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D54" s="27"/>
-    </row>
-    <row r="55" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D55" s="27"/>
-    </row>
-    <row r="56" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D56" s="27"/>
-    </row>
-    <row r="57" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D57" s="27"/>
-    </row>
-    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D58" s="27"/>
-    </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="27"/>
+      <c r="D53" s="25"/>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C54" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="25"/>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D55" s="25"/>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D56" s="25"/>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D57" s="25"/>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D58" s="25"/>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D59" s="25"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I3:I9">
-    <cfRule type="beginsWith" dxfId="1" priority="1" operator="beginsWith" text="Not">
+  <conditionalFormatting sqref="I3:I16">
+    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="Not">
       <formula>LEFT(I3,LEN("Not"))="Not"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="2" operator="beginsWith" text="Selected">
+    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="Selected">
       <formula>LEFT(I3,LEN("Selected"))="Selected"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C47" r:id="rId1" xr:uid="{7087AB48-DBC8-F449-8CDC-FDC7591AB865}"/>
+    <hyperlink ref="C54" r:id="rId1" xr:uid="{7087AB48-DBC8-F449-8CDC-FDC7591AB865}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2400,25 +2569,25 @@
         <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>30</v>
@@ -2429,25 +2598,25 @@
         <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>30</v>
@@ -2455,28 +2624,28 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>30</v>
@@ -2484,88 +2653,118 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="33" t="s">
-        <v>111</v>
+      <c r="B8" s="30" t="s">
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="33"/>
+      <c r="B9" s="30" t="s">
+        <v>104</v>
+      </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="33"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -2576,7 +2775,7 @@
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="33"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2587,7 +2786,7 @@
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="33"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2598,7 +2797,7 @@
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="33"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -2609,7 +2808,7 @@
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="33"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -2620,7 +2819,7 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="33"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -2631,7 +2830,7 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="33"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -2642,7 +2841,7 @@
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="33"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2653,7 +2852,7 @@
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="33"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -2664,7 +2863,7 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="33"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2675,7 +2874,7 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="33"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -2686,7 +2885,7 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="33"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -2697,10 +2896,10 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="34"/>
+      <c r="B22" s="31"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="34"/>
+      <c r="B23" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2710,7 +2909,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:AP31"/>
+  <dimension ref="B2:AP30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -2760,666 +2959,674 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="24" x14ac:dyDescent="0.3">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="60" t="s">
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62" t="s">
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="63"/>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="65" t="s">
+      <c r="W2" s="60"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="66"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="66"/>
-      <c r="AF2" s="66"/>
-      <c r="AG2" s="66"/>
-      <c r="AH2" s="66"/>
-      <c r="AI2" s="66"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="67"/>
-      <c r="AL2" s="68" t="s">
+      <c r="Z2" s="63"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="63"/>
+      <c r="AF2" s="63"/>
+      <c r="AG2" s="63"/>
+      <c r="AH2" s="63"/>
+      <c r="AI2" s="63"/>
+      <c r="AJ2" s="63"/>
+      <c r="AK2" s="64"/>
+      <c r="AL2" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="69"/>
-      <c r="AO2" s="69"/>
-      <c r="AP2" s="70"/>
+      <c r="AM2" s="66"/>
+      <c r="AN2" s="66"/>
+      <c r="AO2" s="66"/>
+      <c r="AP2" s="67"/>
     </row>
     <row r="3" spans="2:42" ht="24" x14ac:dyDescent="0.2">
-      <c r="B3" s="57"/>
-      <c r="C3" s="71" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="74" t="s">
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="40" t="s">
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="48" t="s">
+      <c r="O3" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="U3" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="51" t="s">
+      <c r="W3" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="X3" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y3" s="73" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="73"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD3" s="74"/>
+      <c r="AE3" s="74"/>
+      <c r="AF3" s="74"/>
+      <c r="AG3" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH3" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI3" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ3" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL3" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM3" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN3" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO3" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP3" s="32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:42" ht="61" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="75"/>
+      <c r="C4" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="M4" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="76"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="S4" s="78"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC4" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD4" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE4" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF4" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG4" s="82"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="82"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="82"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="53"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="36"/>
+    </row>
+    <row r="5" spans="2:42" s="43" customFormat="1" ht="145" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="O5" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="P5" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q5" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="R5" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="S5" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="T5" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="U5" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="V5" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="W5" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="X5" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y5" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z5" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC5" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD5" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE5" s="42"/>
+      <c r="AF5" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="T3" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="U3" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="W3" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="X3" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y3" s="76" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z3" s="76"/>
-      <c r="AA3" s="76"/>
-      <c r="AB3" s="76"/>
-      <c r="AC3" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD3" s="77"/>
-      <c r="AE3" s="77"/>
-      <c r="AF3" s="77"/>
-      <c r="AG3" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH3" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI3" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="AM3" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN3" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO3" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="AP3" s="35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="2:42" ht="61" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="78"/>
-      <c r="C4" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="42" t="s">
+      <c r="AG5" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH5" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="AI5" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AK5" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL5" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="AM5" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN5" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO5" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="AP5" s="41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="2:42" s="43" customFormat="1" ht="192" x14ac:dyDescent="0.2">
+      <c r="B6" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="O6" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="P6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="R6" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="S6" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="T6" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="U6" s="46"/>
+      <c r="V6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="W6" s="46"/>
+      <c r="X6" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y6" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z6" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA6" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB6" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC6" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="J4" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="K4" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="L4" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="M4" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="79"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="R4" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="S4" s="81"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="81"/>
-      <c r="V4" s="83"/>
-      <c r="W4" s="84"/>
-      <c r="X4" s="83"/>
-      <c r="Y4" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA4" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB4" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC4" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD4" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE4" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF4" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG4" s="85"/>
-      <c r="AH4" s="86"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="86"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="39"/>
-      <c r="AM4" s="56"/>
-      <c r="AN4" s="39"/>
-      <c r="AO4" s="56"/>
-      <c r="AP4" s="39"/>
-    </row>
-    <row r="5" spans="2:42" s="46" customFormat="1" ht="145" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="87" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="H5" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="I5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="O5" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="P5" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q5" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="R5" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="S5" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="T5" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="U5" s="45" t="s">
+      <c r="AD6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF6" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG6" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH6" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI6" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ6" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="AK6" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL6" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="AM6" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN6" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO6" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP6" s="41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="2:42" s="43" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="B7" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="O7" s="41"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="S7" s="41"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="41"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="41"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="41"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="41"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="41"/>
+      <c r="AJ7" s="41"/>
+      <c r="AK7" s="41"/>
+      <c r="AL7" s="41"/>
+      <c r="AM7" s="41"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="41"/>
+      <c r="AP7" s="41"/>
+    </row>
+    <row r="8" spans="2:42" s="43" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="V5" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="W5" s="45" t="s">
+      <c r="D8" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="L8" s="88" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="R8" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="S8" s="46"/>
+      <c r="T8" s="87"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="W8" s="41"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="X5" s="45" t="s">
+      <c r="Z8" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA8" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC8" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AE8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF8" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG8" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="Y5" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z5" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA5" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB5" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC5" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD5" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="AG5" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="AH5" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI5" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ5" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="AK5" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL5" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="AM5" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="AN5" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="AO5" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="AP5" s="44" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="2:42" s="46" customFormat="1" ht="192" x14ac:dyDescent="0.2">
-      <c r="B6" s="88" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="L6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="M6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="N6" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="O6" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="P6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q6" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="R6" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="S6" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="T6" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="U6" s="49"/>
-      <c r="V6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="W6" s="49"/>
-      <c r="X6" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y6" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z6" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA6" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB6" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC6" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF6" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG6" s="44" t="s">
+      <c r="AH8" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI8" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="AH6" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI6" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ6" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="AK6" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL6" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM6" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AN6" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="AO6" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="AP6" s="44" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="2:42" s="46" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="B7" s="88" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="O7" s="44"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="44"/>
-      <c r="AF7" s="44"/>
-      <c r="AG7" s="44"/>
-      <c r="AH7" s="44"/>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="44"/>
-      <c r="AK7" s="44"/>
-      <c r="AL7" s="44"/>
-      <c r="AM7" s="44"/>
-      <c r="AN7" s="44"/>
-      <c r="AO7" s="44"/>
-      <c r="AP7" s="44"/>
-    </row>
-    <row r="8" spans="2:42" s="46" customFormat="1" ht="230" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="90" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="N8" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="O8" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>170</v>
-      </c>
-      <c r="T8" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="U8" s="44" t="s">
-        <v>170</v>
-      </c>
-      <c r="V8" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="W8" s="44"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="44"/>
-      <c r="Z8" s="44"/>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="44"/>
-      <c r="AC8" s="44"/>
-      <c r="AD8" s="44"/>
-      <c r="AE8" s="44"/>
-      <c r="AF8" s="44"/>
-      <c r="AG8" s="44"/>
-      <c r="AH8" s="44"/>
-      <c r="AI8" s="44"/>
-      <c r="AJ8" s="44"/>
-      <c r="AK8" s="44"/>
-      <c r="AL8" s="44"/>
-      <c r="AM8" s="44"/>
-      <c r="AN8" s="44"/>
-      <c r="AO8" s="44"/>
-      <c r="AP8" s="44"/>
-    </row>
-    <row r="9" spans="2:42" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="44"/>
-      <c r="AE9" s="44"/>
-      <c r="AF9" s="44"/>
-      <c r="AG9" s="44"/>
-      <c r="AH9" s="44"/>
-      <c r="AI9" s="44"/>
-      <c r="AJ9" s="44"/>
-      <c r="AK9" s="44"/>
-      <c r="AL9" s="44"/>
-      <c r="AM9" s="44"/>
-      <c r="AN9" s="44"/>
-      <c r="AO9" s="44"/>
-      <c r="AP9" s="44"/>
-    </row>
-    <row r="10" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL8" s="41"/>
+      <c r="AM8" s="41"/>
+      <c r="AN8" s="41"/>
+      <c r="AO8" s="41"/>
+      <c r="AP8" s="41"/>
+    </row>
+    <row r="9" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AG9" s="19"/>
+      <c r="AH9" s="19"/>
+      <c r="AI9" s="19"/>
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="19"/>
+      <c r="AP9" s="19"/>
+    </row>
+    <row r="10" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -3462,7 +3669,7 @@
       <c r="AO10" s="19"/>
       <c r="AP10" s="19"/>
     </row>
-    <row r="11" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
@@ -3505,7 +3712,7 @@
       <c r="AO11" s="19"/>
       <c r="AP11" s="19"/>
     </row>
-    <row r="12" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
@@ -3548,7 +3755,7 @@
       <c r="AO12" s="19"/>
       <c r="AP12" s="19"/>
     </row>
-    <row r="13" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
@@ -3591,7 +3798,7 @@
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
     </row>
-    <row r="14" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -3634,7 +3841,7 @@
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
     </row>
-    <row r="15" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -3677,7 +3884,7 @@
       <c r="AO15" s="19"/>
       <c r="AP15" s="19"/>
     </row>
-    <row r="16" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -3720,7 +3927,7 @@
       <c r="AO16" s="19"/>
       <c r="AP16" s="19"/>
     </row>
-    <row r="17" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
@@ -3763,7 +3970,7 @@
       <c r="AO17" s="19"/>
       <c r="AP17" s="19"/>
     </row>
-    <row r="18" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
@@ -3806,7 +4013,7 @@
       <c r="AO18" s="19"/>
       <c r="AP18" s="19"/>
     </row>
-    <row r="19" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
@@ -3849,7 +4056,7 @@
       <c r="AO19" s="19"/>
       <c r="AP19" s="19"/>
     </row>
-    <row r="20" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
@@ -3892,7 +4099,7 @@
       <c r="AO20" s="19"/>
       <c r="AP20" s="19"/>
     </row>
-    <row r="21" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -3935,7 +4142,7 @@
       <c r="AO21" s="19"/>
       <c r="AP21" s="19"/>
     </row>
-    <row r="22" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -3978,7 +4185,7 @@
       <c r="AO22" s="19"/>
       <c r="AP22" s="19"/>
     </row>
-    <row r="23" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -4021,7 +4228,7 @@
       <c r="AO23" s="19"/>
       <c r="AP23" s="19"/>
     </row>
-    <row r="24" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -4064,7 +4271,7 @@
       <c r="AO24" s="19"/>
       <c r="AP24" s="19"/>
     </row>
-    <row r="25" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -4107,7 +4314,7 @@
       <c r="AO25" s="19"/>
       <c r="AP25" s="19"/>
     </row>
-    <row r="26" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
@@ -4150,7 +4357,7 @@
       <c r="AO26" s="19"/>
       <c r="AP26" s="19"/>
     </row>
-    <row r="27" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -4193,7 +4400,7 @@
       <c r="AO27" s="19"/>
       <c r="AP27" s="19"/>
     </row>
-    <row r="28" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -4236,7 +4443,7 @@
       <c r="AO28" s="19"/>
       <c r="AP28" s="19"/>
     </row>
-    <row r="29" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -4279,7 +4486,7 @@
       <c r="AO29" s="19"/>
       <c r="AP29" s="19"/>
     </row>
-    <row r="30" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -4322,49 +4529,6 @@
       <c r="AO30" s="19"/>
       <c r="AP30" s="19"/>
     </row>
-    <row r="31" spans="2:42" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="19"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="19"/>
-      <c r="AB31" s="19"/>
-      <c r="AC31" s="19"/>
-      <c r="AD31" s="19"/>
-      <c r="AE31" s="19"/>
-      <c r="AF31" s="19"/>
-      <c r="AG31" s="19"/>
-      <c r="AH31" s="19"/>
-      <c r="AI31" s="19"/>
-      <c r="AJ31" s="19"/>
-      <c r="AK31" s="19"/>
-      <c r="AL31" s="19"/>
-      <c r="AM31" s="19"/>
-      <c r="AN31" s="19"/>
-      <c r="AO31" s="19"/>
-      <c r="AP31" s="19"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="AL3:AL4"/>

--- a/literature-management.xlsx
+++ b/literature-management.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jay/phd/papers/sok - a survey on software power monitoring tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE64065-D85E-B646-827F-AA68693ADDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22021DDF-0178-9344-BA41-183B4442BB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29920" windowHeight="18560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tools" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="196">
   <si>
     <t>Year</t>
   </si>
@@ -198,9 +198,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Model-based </t>
-  </si>
-  <si>
     <t>CPU</t>
   </si>
   <si>
@@ -355,12 +352,6 @@
   </si>
   <si>
     <t>Backward Snawballing</t>
-  </si>
-  <si>
-    <t>yes (To be discussed : need to dive in a bit more)</t>
-  </si>
-  <si>
-    <t>yes ((To be discussed : need to dive in a bit more)</t>
   </si>
   <si>
     <t>Case Studies</t>
@@ -668,6 +659,51 @@
   </si>
   <si>
     <t>Noureddine, Adel. (2021) 2022. ‘PowerJoular and JoularJX: Multi-Platform Software Power Monitoring Tools’. In Proceedings of the 18th International Conference on Intelligent Environments, Ada. Intelligent Environments. March 22; IEEE, released. https://doi.org/10.1109/IE54923.2022.9826760.</t>
+  </si>
+  <si>
+    <t>SmartWatts</t>
+  </si>
+  <si>
+    <t>from Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+Guillaume Fieni, Romain Rouvoy, and Lionel Seinturier. “SmartWatts: self-calibrating software-defined power meter for containers”. en. In: 2020 20th IEEE/ACM International Symposium on Cluster, Cloud and Internet Computing (CCGRID). Melbourne, Australia: IEEE, May 2020, pp. 479–488. ISBN: 978-172816-095-5. DOI: 10 . 1109 / CCGrid49817 . 2020 . 00 45.</t>
+  </si>
+  <si>
+    <t>from Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+Franz Christian Heinrich et al. “Predicting the energyconsumption of MPI applications at scale using only a single node”. In: 2017 IEEE International Conference on Cluster Computing (CLUSTER). Sept. 2017, pp. 92102. DOI: 10.1109/CLUSTER.2017.66.</t>
+  </si>
+  <si>
+    <t>Code-Carbon</t>
+  </si>
+  <si>
+    <t>from  Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+Victor Schmidt et al. “CodeCarbon: estimate and track carbon emissions from machine learning computing”. In: Zenodo (2021).</t>
+  </si>
+  <si>
+    <t>Likwid</t>
+  </si>
+  <si>
+    <t>from   Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+J. Treibig, G. Hager, and G. Wellein. “LIKWID: a lightweight performance-oriented tool suite for x86 multicore environments”. In: Proceedings of PSTI2010, the First International Workshop on Parallel Software Tools and Tool Infrastructures. San Diego CA, 2010.</t>
+  </si>
+  <si>
+    <t>1Hz (Max 28Hz If modified as in (Raffin and Trystram 2024))</t>
+  </si>
+  <si>
+    <t>~Monitoring Cycle of 1s mentioned in (Noureddine et al. 2012)</t>
+  </si>
+  <si>
+    <t>Model-based (TDP)</t>
+  </si>
+  <si>
+    <t>Reported in (Noureddine et al. 2012; (Noureddine et al. 2015))</t>
+  </si>
+  <si>
+    <t>Two methods available: 
+1) Statistical Sampling of Call Stack --&gt; No Code Modification
+2) Source Code Instrumentation (i.e. time markers around functions)</t>
+  </si>
+  <si>
+    <t>yes (Java Applications)</t>
   </si>
 </sst>
 </file>
@@ -1059,27 +1095,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1096,65 +1111,161 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1164,98 +1275,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1277,25 +1303,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="0.34998626667073579"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1315,6 +1322,25 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1488,13 +1514,13 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{DF00C389-F294-FB48-80B0-022781D38C47}">
-      <tableStyleElement type="wholeTable" dxfId="19"/>
+      <tableStyleElement type="wholeTable" dxfId="18"/>
     </tableStyle>
     <tableStyle name="Table Style 2" pivot="0" count="4" xr9:uid="{66177898-DED3-9C47-8DA6-ABD521A19111}">
-      <tableStyleElement type="wholeTable" dxfId="18"/>
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="secondRowStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1509,18 +1535,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C9355DD-35BE-3D46-8331-B67246AE3C74}" name="Table1" displayName="Table1" ref="C2:K22" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C9355DD-35BE-3D46-8331-B67246AE3C74}" name="Table1" displayName="Table1" ref="C2:K22" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="C2:K22" xr:uid="{1C9355DD-35BE-3D46-8331-B67246AE3C74}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B697189A-DF2B-4341-9FF4-7259FA9252F8}" name="Tool Name" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{F3B719A6-5185-6144-A373-7DD05C5FE758}" name="References" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{271ED028-8F14-D741-A569-E2FEB926BB1C}" name="Year" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{B7FF3EF8-B658-904B-8045-D98673D5126F}" name="Authors/Institution" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{63D16556-412F-8B4C-BF7C-5FF77216838E}" name="Discovery Method" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{946E4FD2-8FE0-9345-A39D-83A4386577DF}" name="Discovered From" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{DF93B5C3-BD8E-D543-8F4C-AC0C5199BC07}" name="Selection Status" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{03969A93-C0C5-BB4C-ACA8-090EAA97265A}" name="Exclusion Reason" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{01558EB7-81C3-6642-A7E2-29E574F37760}" name="Short Description" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{B697189A-DF2B-4341-9FF4-7259FA9252F8}" name="Tool Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{F3B719A6-5185-6144-A373-7DD05C5FE758}" name="References" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{271ED028-8F14-D741-A569-E2FEB926BB1C}" name="Year" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B7FF3EF8-B658-904B-8045-D98673D5126F}" name="Authors/Institution" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{63D16556-412F-8B4C-BF7C-5FF77216838E}" name="Discovery Method" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{946E4FD2-8FE0-9345-A39D-83A4386577DF}" name="Discovered From" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{DF93B5C3-BD8E-D543-8F4C-AC0C5199BC07}" name="Selection Status" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{03969A93-C0C5-BB4C-ACA8-090EAA97265A}" name="Exclusion Reason" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{01558EB7-81C3-6642-A7E2-29E574F37760}" name="Short Description" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1811,7 +1837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K59"/>
+  <dimension ref="B2:K113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="11" bestFit="1" customWidth="1"/>
@@ -1863,7 +1889,7 @@
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="89" t="s">
+      <c r="D3" s="46" t="s">
         <v>51</v>
       </c>
       <c r="E3" s="8">
@@ -1885,7 +1911,7 @@
         <v>35</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="80" x14ac:dyDescent="0.2">
@@ -1893,7 +1919,7 @@
       <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="89" t="s">
+      <c r="D4" s="46" t="s">
         <v>52</v>
       </c>
       <c r="E4" s="6">
@@ -1921,16 +1947,16 @@
     <row r="5" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B5"/>
       <c r="C5" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="89" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="46" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="6">
         <v>2012</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>53</v>
@@ -1945,7 +1971,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="48" x14ac:dyDescent="0.2">
@@ -1953,29 +1979,29 @@
       <c r="C6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>95</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>96</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="80" x14ac:dyDescent="0.2">
@@ -1983,20 +2009,20 @@
       <c r="C7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="46" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="8">
         <v>2020</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>30</v>
@@ -2005,52 +2031,52 @@
         <v>35</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B8"/>
       <c r="C8" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="89" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="46" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="6">
         <v>2017</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="272" x14ac:dyDescent="0.2">
       <c r="B9"/>
       <c r="C9" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="89" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>104</v>
       </c>
       <c r="E9" s="6">
         <v>2025</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>53</v>
@@ -2059,13 +2085,13 @@
         <v>35</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="272" x14ac:dyDescent="0.2">
@@ -2073,20 +2099,20 @@
       <c r="C10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="92" t="s">
-        <v>184</v>
+      <c r="D10" s="49" t="s">
+        <v>181</v>
       </c>
       <c r="E10" s="6">
         <v>2015</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>30</v>
@@ -2095,7 +2121,7 @@
         <v>35</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="335" x14ac:dyDescent="0.2">
@@ -2103,20 +2129,20 @@
       <c r="C11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="91" t="s">
-        <v>183</v>
+      <c r="D11" s="48" t="s">
+        <v>180</v>
       </c>
       <c r="E11" s="6">
         <v>2015</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>30</v>
@@ -2125,7 +2151,7 @@
         <v>35</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="32" x14ac:dyDescent="0.2">
@@ -2133,18 +2159,18 @@
       <c r="C12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="91" t="s">
-        <v>185</v>
+      <c r="D12" s="48" t="s">
+        <v>182</v>
       </c>
       <c r="E12" s="6">
         <v>2021</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>30</v>
@@ -2156,13 +2182,13 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13"/>
-      <c r="D13" s="91"/>
+      <c r="D13" s="48"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="91"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="10"/>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
@@ -2174,7 +2200,7 @@
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
-      <c r="D15" s="91"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="10"/>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
@@ -2186,7 +2212,7 @@
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="91"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="10"/>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
@@ -2198,7 +2224,7 @@
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="91"/>
+      <c r="D17" s="48"/>
       <c r="E17" s="10"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
@@ -2209,7 +2235,7 @@
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="91"/>
+      <c r="D18" s="48"/>
       <c r="E18" s="10"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
@@ -2220,7 +2246,7 @@
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="91"/>
+      <c r="D19" s="48"/>
       <c r="E19" s="10"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
@@ -2231,7 +2257,7 @@
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="91"/>
+      <c r="D20" s="48"/>
       <c r="E20" s="10"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
@@ -2242,8 +2268,8 @@
     <row r="21" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="91" t="s">
-        <v>105</v>
+      <c r="D21" s="48" t="s">
+        <v>102</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="18"/>
@@ -2255,7 +2281,7 @@
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="91"/>
+      <c r="D22" s="48"/>
       <c r="E22" s="10"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
@@ -2322,7 +2348,7 @@
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="10"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="25"/>
+      <c r="D29" s="48"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
       <c r="H29" s="15"/>
@@ -2332,8 +2358,8 @@
       <c r="C30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="25" t="s">
-        <v>171</v>
+      <c r="D30" s="48" t="s">
+        <v>168</v>
       </c>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
@@ -2343,21 +2369,21 @@
       <c r="C31" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="25" t="s">
-        <v>171</v>
+      <c r="D31" s="48" t="s">
+        <v>168</v>
       </c>
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="10"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="25"/>
+      <c r="D32" s="48"/>
       <c r="G32" s="18"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="10"/>
       <c r="C33" s="6"/>
-      <c r="D33" s="25"/>
+      <c r="D33" s="48"/>
       <c r="G33" s="18"/>
     </row>
     <row r="34" spans="2:7" ht="32" x14ac:dyDescent="0.2">
@@ -2365,145 +2391,330 @@
       <c r="C34" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="25" t="s">
-        <v>171</v>
+      <c r="D34" s="48" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="C35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>171</v>
+      <c r="D35" s="48" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="C36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="25" t="s">
-        <v>171</v>
+      <c r="D36" s="48" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="C37" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="25" t="s">
-        <v>171</v>
+      <c r="D37" s="48" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="C38" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="25" t="s">
-        <v>171</v>
+      <c r="D38" s="48" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C39" s="6"/>
-      <c r="D39" s="25"/>
+      <c r="D39" s="48"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D40" s="48"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D41" s="25"/>
+      <c r="D41" s="48"/>
     </row>
     <row r="42" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="C42" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
+      </c>
+      <c r="D42" s="48" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D43" s="25"/>
+      <c r="D43" s="48"/>
     </row>
     <row r="44" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C44" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C45" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>166</v>
+        <v>164</v>
+      </c>
+      <c r="D45" s="48" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D46" s="25"/>
+      <c r="D46" s="48"/>
     </row>
     <row r="47" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C47" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="D47" s="48" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C48" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D48" s="25" t="s">
         <v>166</v>
+      </c>
+      <c r="D48" s="48" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="3:4" ht="16" x14ac:dyDescent="0.2">
       <c r="C49" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>166</v>
+        <v>167</v>
+      </c>
+      <c r="D49" s="48" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D50" s="25"/>
+      <c r="D50" s="48"/>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D51" s="25"/>
+      <c r="D51" s="48"/>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D52" s="25"/>
+      <c r="D52" s="48"/>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="25"/>
+      <c r="D53" s="48"/>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C54" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="D54" s="25"/>
+      <c r="C54" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="48"/>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D55" s="25"/>
+      <c r="D55" s="48"/>
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D56" s="25"/>
+      <c r="D56" s="48"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D57" s="25"/>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D58" s="25"/>
+      <c r="D57" s="48"/>
+    </row>
+    <row r="58" spans="3:4" ht="48" x14ac:dyDescent="0.2">
+      <c r="C58" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D58" s="48" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="25"/>
+      <c r="D59" s="48"/>
+    </row>
+    <row r="60" spans="3:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="C60" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60" s="48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D61" s="48"/>
+    </row>
+    <row r="62" spans="3:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="C62" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62" s="48" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="C63" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="48" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D64" s="48"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D65" s="48"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D66" s="48"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D67" s="48"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D68" s="48"/>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D69" s="48"/>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D70" s="48"/>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D71" s="48"/>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="48"/>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D73" s="48"/>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D74" s="48"/>
+    </row>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D75" s="48"/>
+    </row>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D76" s="48"/>
+    </row>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D77" s="48"/>
+    </row>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D78" s="48"/>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="48"/>
+    </row>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D80" s="48"/>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D81" s="48"/>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D82" s="48"/>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D83" s="48"/>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D84" s="48"/>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D85" s="48"/>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D86" s="48"/>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D87" s="48"/>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D88" s="48"/>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D89" s="48"/>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D90" s="48"/>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D91" s="48"/>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D92" s="48"/>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D93" s="48"/>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D94" s="48"/>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D95" s="48"/>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D96" s="48"/>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D97" s="48"/>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D98" s="48"/>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D99" s="48"/>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D100" s="48"/>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D101" s="48"/>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D102" s="48"/>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D103" s="48"/>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D104" s="48"/>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D105" s="48"/>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D106" s="48"/>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D107" s="48"/>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D108" s="48"/>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D109" s="48"/>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D110" s="48"/>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D111" s="48"/>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D112" s="48"/>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D113" s="48"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I3:I16">
-    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="Not">
+    <cfRule type="beginsWith" dxfId="1" priority="1" operator="beginsWith" text="Not">
       <formula>LEFT(I3,LEN("Not"))="Not"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="Selected">
+    <cfRule type="beginsWith" dxfId="0" priority="2" operator="beginsWith" text="Selected">
       <formula>LEFT(I3,LEN("Selected"))="Selected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2569,7 +2780,7 @@
         <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>55</v>
@@ -2578,16 +2789,16 @@
         <v>55</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>30</v>
@@ -2607,16 +2818,16 @@
         <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>30</v>
@@ -2633,19 +2844,19 @@
         <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>30</v>
@@ -2659,25 +2870,25 @@
         <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -2694,16 +2905,16 @@
         <v>55</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>30</v>
@@ -2711,13 +2922,13 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="30" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>55</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>55</v>
@@ -2726,25 +2937,25 @@
         <v>55</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="30" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>55</v>
@@ -2753,15 +2964,17 @@
         <v>55</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="J9" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="30"/>
@@ -2959,631 +3172,689 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="24" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57" t="s">
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="59" t="s">
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="62" t="s">
+      <c r="W2" s="55"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="63"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
-      <c r="AH2" s="63"/>
-      <c r="AI2" s="63"/>
-      <c r="AJ2" s="63"/>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="65" t="s">
+      <c r="Z2" s="58"/>
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="58"/>
+      <c r="AC2" s="58"/>
+      <c r="AD2" s="58"/>
+      <c r="AE2" s="58"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="58"/>
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="58"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="66"/>
-      <c r="AN2" s="66"/>
-      <c r="AO2" s="66"/>
-      <c r="AP2" s="67"/>
+      <c r="AM2" s="91"/>
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="91"/>
+      <c r="AP2" s="92"/>
     </row>
     <row r="3" spans="2:42" ht="24" x14ac:dyDescent="0.2">
-      <c r="B3" s="54"/>
-      <c r="C3" s="68" t="s">
+      <c r="B3" s="60"/>
+      <c r="C3" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="71" t="s">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="37" t="s">
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="45" t="s">
+      <c r="O3" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="P3" s="33" t="s">
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="T3" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="48" t="s">
+      <c r="U3" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y3" s="84" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="85" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH3" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI3" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK3" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL3" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM3" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN3" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO3" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP3" s="50" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="2:42" ht="61" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="61"/>
+      <c r="C4" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="T3" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="U3" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="W3" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="X3" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y3" s="73" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="73"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="74" t="s">
+      <c r="H4" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="70"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="S4" s="74"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="74"/>
+      <c r="V4" s="87"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="87"/>
+      <c r="Y4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC4" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="AD3" s="74"/>
-      <c r="AE3" s="74"/>
-      <c r="AF3" s="74"/>
-      <c r="AG3" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH3" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI3" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ3" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK3" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL3" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM3" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN3" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO3" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="AP3" s="32" t="s">
+      <c r="AD4" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE4" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF4" s="40" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="2:42" ht="61" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="75"/>
-      <c r="C4" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="39" t="s">
+      <c r="AG4" s="81"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="81"/>
+      <c r="AL4" s="51"/>
+      <c r="AM4" s="53"/>
+      <c r="AN4" s="51"/>
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="51"/>
+    </row>
+    <row r="5" spans="2:42" s="36" customFormat="1" ht="145" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="O5" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="U5" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="W5" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="X5" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y5" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z5" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC5" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD5" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE5" s="35"/>
+      <c r="AF5" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG5" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH5" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI5" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL5" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM5" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="AN5" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO5" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="AP5" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="2:42" s="36" customFormat="1" ht="192" x14ac:dyDescent="0.2">
+      <c r="B6" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="U6" s="38"/>
+      <c r="V6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="W6" s="38"/>
+      <c r="X6" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y6" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA6" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB6" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC6" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG6" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ6" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK6" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL6" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="AM6" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN6" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO6" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP6" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="2:42" s="36" customFormat="1" ht="160" x14ac:dyDescent="0.2">
+      <c r="B7" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="M7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="O7" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="P7" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q7" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="S7" s="38"/>
+      <c r="T7" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="U7" s="38"/>
+      <c r="V7" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z7" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD7" s="34"/>
+      <c r="AE7" s="34"/>
+      <c r="AF7" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AI7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AK7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL7" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="AM7" s="34"/>
+      <c r="AN7" s="34"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="34"/>
+    </row>
+    <row r="8" spans="2:42" s="36" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="K4" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="L4" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="M4" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="76"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="R4" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="S4" s="78"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="78"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="81"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA4" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB4" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="AC4" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD4" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE4" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF4" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG4" s="82"/>
-      <c r="AH4" s="83"/>
-      <c r="AI4" s="82"/>
-      <c r="AJ4" s="83"/>
-      <c r="AK4" s="82"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="53"/>
-      <c r="AN4" s="36"/>
-      <c r="AO4" s="53"/>
-      <c r="AP4" s="36"/>
-    </row>
-    <row r="5" spans="2:42" s="43" customFormat="1" ht="145" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="N5" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="O5" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="P5" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q5" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="R5" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="S5" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="T5" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="U5" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="V5" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="W5" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="X5" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y5" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z5" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC5" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="AD5" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE5" s="42"/>
-      <c r="AF5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG5" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH5" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI5" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="AJ5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AK5" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AL5" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="AM5" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="AN5" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO5" s="42" t="s">
+      <c r="J8" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="O8" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q8" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="AP5" s="41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="2:42" s="43" customFormat="1" ht="192" x14ac:dyDescent="0.2">
-      <c r="B6" s="85" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>137</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="G6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="J6" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="L6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="M6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="N6" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="O6" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="P6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q6" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="R6" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="S6" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="T6" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="U6" s="46"/>
-      <c r="V6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="W6" s="46"/>
-      <c r="X6" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y6" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z6" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA6" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB6" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC6" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="AD6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF6" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG6" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH6" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI6" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ6" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="AK6" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="AL6" s="41" t="s">
+      <c r="R8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="S8" s="38"/>
+      <c r="T8" s="44"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="W8" s="34"/>
+      <c r="X8" s="34"/>
+      <c r="Y8" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="AM6" s="41" t="s">
+      <c r="Z8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF8" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG8" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="AN6" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO6" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="AP6" s="41" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="2:42" s="43" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="B7" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41" t="s">
+      <c r="AH8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ8" s="34"/>
+      <c r="AK8" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="O7" s="41"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="41"/>
-      <c r="AA7" s="41"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="41"/>
-      <c r="AD7" s="41"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="41"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="41"/>
-      <c r="AJ7" s="41"/>
-      <c r="AK7" s="41"/>
-      <c r="AL7" s="41"/>
-      <c r="AM7" s="41"/>
-      <c r="AN7" s="41"/>
-      <c r="AO7" s="41"/>
-      <c r="AP7" s="41"/>
-    </row>
-    <row r="8" spans="2:42" s="43" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="L8" s="88" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q8" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="R8" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="S8" s="46"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z8" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA8" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC8" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF8" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG8" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH8" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI8" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ8" s="41"/>
-      <c r="AK8" s="41" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL8" s="41"/>
-      <c r="AM8" s="41"/>
-      <c r="AN8" s="41"/>
-      <c r="AO8" s="41"/>
-      <c r="AP8" s="41"/>
-    </row>
-    <row r="9" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AL8" s="34"/>
+      <c r="AM8" s="34"/>
+      <c r="AN8" s="34"/>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="34"/>
+    </row>
+    <row r="9" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -3626,7 +3897,7 @@
       <c r="AO9" s="19"/>
       <c r="AP9" s="19"/>
     </row>
-    <row r="10" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -3669,7 +3940,7 @@
       <c r="AO10" s="19"/>
       <c r="AP10" s="19"/>
     </row>
-    <row r="11" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
@@ -3712,7 +3983,7 @@
       <c r="AO11" s="19"/>
       <c r="AP11" s="19"/>
     </row>
-    <row r="12" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
@@ -3755,7 +4026,7 @@
       <c r="AO12" s="19"/>
       <c r="AP12" s="19"/>
     </row>
-    <row r="13" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
@@ -3798,7 +4069,7 @@
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
     </row>
-    <row r="14" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -3841,7 +4112,7 @@
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
     </row>
-    <row r="15" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -3884,7 +4155,7 @@
       <c r="AO15" s="19"/>
       <c r="AP15" s="19"/>
     </row>
-    <row r="16" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -3927,7 +4198,7 @@
       <c r="AO16" s="19"/>
       <c r="AP16" s="19"/>
     </row>
-    <row r="17" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
       <c r="D17" s="19"/>
@@ -3970,7 +4241,7 @@
       <c r="AO17" s="19"/>
       <c r="AP17" s="19"/>
     </row>
-    <row r="18" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
       <c r="D18" s="19"/>
@@ -4013,7 +4284,7 @@
       <c r="AO18" s="19"/>
       <c r="AP18" s="19"/>
     </row>
-    <row r="19" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
       <c r="D19" s="19"/>
@@ -4056,7 +4327,7 @@
       <c r="AO19" s="19"/>
       <c r="AP19" s="19"/>
     </row>
-    <row r="20" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
@@ -4099,7 +4370,7 @@
       <c r="AO20" s="19"/>
       <c r="AP20" s="19"/>
     </row>
-    <row r="21" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -4142,7 +4413,7 @@
       <c r="AO21" s="19"/>
       <c r="AP21" s="19"/>
     </row>
-    <row r="22" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -4185,7 +4456,7 @@
       <c r="AO22" s="19"/>
       <c r="AP22" s="19"/>
     </row>
-    <row r="23" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -4228,7 +4499,7 @@
       <c r="AO23" s="19"/>
       <c r="AP23" s="19"/>
     </row>
-    <row r="24" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -4271,7 +4542,7 @@
       <c r="AO24" s="19"/>
       <c r="AP24" s="19"/>
     </row>
-    <row r="25" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -4314,7 +4585,7 @@
       <c r="AO25" s="19"/>
       <c r="AP25" s="19"/>
     </row>
-    <row r="26" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
@@ -4357,7 +4628,7 @@
       <c r="AO26" s="19"/>
       <c r="AP26" s="19"/>
     </row>
-    <row r="27" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -4400,7 +4671,7 @@
       <c r="AO27" s="19"/>
       <c r="AP27" s="19"/>
     </row>
-    <row r="28" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -4443,7 +4714,7 @@
       <c r="AO28" s="19"/>
       <c r="AP28" s="19"/>
     </row>
-    <row r="29" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -4486,7 +4757,7 @@
       <c r="AO29" s="19"/>
       <c r="AP29" s="19"/>
     </row>
-    <row r="30" spans="2:42" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -4531,19 +4802,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="Y2:AK2"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="C2:O2"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="U3:U4"/>
     <mergeCell ref="AN3:AN4"/>
     <mergeCell ref="AP3:AP4"/>
     <mergeCell ref="P2:U2"/>
@@ -4560,6 +4818,19 @@
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="AO3:AO4"/>
     <mergeCell ref="AL2:AP2"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="Y2:AK2"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="C2:O2"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:U4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/literature-management.xlsx
+++ b/literature-management.xlsx
@@ -8,21 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jay/phd/papers/sok - a survey on software power monitoring tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22021DDF-0178-9344-BA41-183B4442BB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F422A9-F1EA-3D47-94FD-B3D26B7BF8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29920" windowHeight="18560" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tools" sheetId="1" r:id="rId1"/>
     <sheet name="Inclusion Exclusion" sheetId="2" r:id="rId2"/>
     <sheet name="Classification" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="260">
   <si>
     <t>Year</t>
   </si>
@@ -291,10 +304,6 @@
   <si>
     <t>Community 
 adoption</t>
-  </si>
-  <si>
-    <t>Architecture-
-Agnostic</t>
   </si>
   <si>
     <t>Embedded 
@@ -642,68 +651,280 @@
     <t>e-Surgeon (= Jalen + PowerAPI)</t>
   </si>
   <si>
-    <t>CERN (Khan et al. 2015)</t>
+    <t>Khan, Kashif, Filip Nybäck, Zhonghong Ou, et al. 2015. Energy Profiling Using IgProf. In Proceedings - 2015 IEEE/ACM 15th International Symposium on Cluster, Cloud, and Grid Computing, CCGrid 2015. https://doi.org/10.1109/CCGrid.2015.118.</t>
+  </si>
+  <si>
+    <t>Liu, Kenan, Gustavo Pinto, and Yu David Liu. 2015. ‘Data-Oriented Characterization of Application-Level Energy Optimization’. In Fundamental Approaches to Software Engineering, edited by Alexander Egyed and Ina Schaefer. Springer. https://doi.org/10.1007/978-3-662-46675-9_21.</t>
+  </si>
+  <si>
+    <t>Noureddine, Adel. (2021) 2022. ‘PowerJoular and JoularJX: Multi-Platform Software Power Monitoring Tools’. In Proceedings of the 18th International Conference on Intelligent Environments, Ada. Intelligent Environments. March 22; IEEE, released. https://doi.org/10.1109/IE54923.2022.9826760.</t>
+  </si>
+  <si>
+    <t>SmartWatts</t>
+  </si>
+  <si>
+    <t>from Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+Guillaume Fieni, Romain Rouvoy, and Lionel Seinturier. “SmartWatts: self-calibrating software-defined power meter for containers”. en. In: 2020 20th IEEE/ACM International Symposium on Cluster, Cloud and Internet Computing (CCGRID). Melbourne, Australia: IEEE, May 2020, pp. 479–488. ISBN: 978-172816-095-5. DOI: 10 . 1109 / CCGrid49817 . 2020 . 00 45.</t>
+  </si>
+  <si>
+    <t>from Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+Franz Christian Heinrich et al. “Predicting the energyconsumption of MPI applications at scale using only a single node”. In: 2017 IEEE International Conference on Cluster Computing (CLUSTER). Sept. 2017, pp. 92102. DOI: 10.1109/CLUSTER.2017.66.</t>
+  </si>
+  <si>
+    <t>Code-Carbon</t>
+  </si>
+  <si>
+    <t>from  Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+Victor Schmidt et al. “CodeCarbon: estimate and track carbon emissions from machine learning computing”. In: Zenodo (2021).</t>
+  </si>
+  <si>
+    <t>Likwid</t>
+  </si>
+  <si>
+    <t>from   Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
+J. Treibig, G. Hager, and G. Wellein. “LIKWID: a lightweight performance-oriented tool suite for x86 multicore environments”. In: Proceedings of PSTI2010, the First International Workshop on Parallel Software Tools and Tool Infrastructures. San Diego CA, 2010.</t>
+  </si>
+  <si>
+    <t>1Hz (Max 28Hz If modified as in (Raffin and Trystram 2024))</t>
+  </si>
+  <si>
+    <t>~Monitoring Cycle of 1s mentioned in (Noureddine et al. 2012)</t>
+  </si>
+  <si>
+    <t>Model-based (TDP)</t>
+  </si>
+  <si>
+    <t>Reported in (Noureddine et al. 2012; (Noureddine et al. 2015))</t>
+  </si>
+  <si>
+    <t>Two methods available: 
+1) Statistical Sampling of Call Stack --&gt; No Code Modification
+2) Source Code Instrumentation (i.e. time markers around functions)</t>
+  </si>
+  <si>
+    <t>yes (Java Applications)</t>
+  </si>
+  <si>
+    <t>Noureddine, Adel</t>
+  </si>
+  <si>
+    <t>Lassi Tuura, Giulio, Mikko Kurkela and Filip Nybäck</t>
   </si>
   <si>
     <t>IgProf is originally an application profiler developed at CERN to analyse performance and memory behaviour of programs, and was later extended with an energy profiling module. This module enables the attribution of energy consumption within a program, typically at the level of functions.
-The approach relies on statistical sampling. At regular intervals, the profiler reads energy values from RAPL (through the PAPI library) and attributes the energy difference to the current execution point. This allows building energy profiles in the same way as traditional performance profiles (e.g., flat profiles (cumulated energy offunction and called sub-function) or call graphs)
+The approach relies on statistical sampling. IgProf is injected into the target application as a shared library at startup, allowing it to operate entirely within the same process address space. It performs statistical sampling using interval timers and signal handlers, which execute in the context of the application thread. At each sampling point, the profiler captures the current call stack and associates it with energy measurements obtained via RAPL (through PAPI), enabling in-process attribution of energy consumption to functions.. This allows building energy profiles in the same way as traditional performance profiles (e.g., flat profiles (cumulated energy offunction and called sub-function) or call graphs)
 One advantage is that IgProf operates entirely in user space and does not require recompilation of the application. This makes it relatively non-intrusive compared to instrumentation-based approaches. It can also handle dynamically loaded libraries, which is useful in complex software stacks.
 In terms of granularity, the tool provides fine-grained attribution at function level, but this is based on sampling and indirect attribution rather than exact measurement. As a result, short-lived code sections (shorter than the RAPL update interval, ~1 ms) may not be measured accurately, and multi-threaded scenarios introduce additional challenges in attributing energy correctly. (Khan et al. 2015)   
 Overall, IgProf can be seen as a sampling-based, hardware-informed energy profiling approach. It offers good integration with performance profiling and low intrusiveness, but with limitations in accuracy for short events and complex concurrent workloads.</t>
   </si>
   <si>
-    <t>Khan, Kashif, Filip Nybäck, Zhonghong Ou, et al. 2015. Energy Profiling Using IgProf. In Proceedings - 2015 IEEE/ACM 15th International Symposium on Cluster, Cloud, and Grid Computing, CCGrid 2015. https://doi.org/10.1109/CCGrid.2015.118.</t>
-  </si>
-  <si>
-    <t>Liu, Kenan, Gustavo Pinto, and Yu David Liu. 2015. ‘Data-Oriented Characterization of Application-Level Energy Optimization’. In Fundamental Approaches to Software Engineering, edited by Alexander Egyed and Ina Schaefer. Springer. https://doi.org/10.1007/978-3-662-46675-9_21.</t>
-  </si>
-  <si>
-    <t>Noureddine, Adel. (2021) 2022. ‘PowerJoular and JoularJX: Multi-Platform Software Power Monitoring Tools’. In Proceedings of the 18th International Conference on Intelligent Environments, Ada. Intelligent Environments. March 22; IEEE, released. https://doi.org/10.1109/IE54923.2022.9826760.</t>
-  </si>
-  <si>
-    <t>SmartWatts</t>
-  </si>
-  <si>
-    <t>from Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
-Guillaume Fieni, Romain Rouvoy, and Lionel Seinturier. “SmartWatts: self-calibrating software-defined power meter for containers”. en. In: 2020 20th IEEE/ACM International Symposium on Cluster, Cloud and Internet Computing (CCGRID). Melbourne, Australia: IEEE, May 2020, pp. 479–488. ISBN: 978-172816-095-5. DOI: 10 . 1109 / CCGrid49817 . 2020 . 00 45.</t>
-  </si>
-  <si>
-    <t>from Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
-Franz Christian Heinrich et al. “Predicting the energyconsumption of MPI applications at scale using only a single node”. In: 2017 IEEE International Conference on Cluster Computing (CLUSTER). Sept. 2017, pp. 92102. DOI: 10.1109/CLUSTER.2017.66.</t>
-  </si>
-  <si>
-    <t>Code-Carbon</t>
-  </si>
-  <si>
-    <t>from  Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
-Victor Schmidt et al. “CodeCarbon: estimate and track carbon emissions from machine learning computing”. In: Zenodo (2021).</t>
-  </si>
-  <si>
-    <t>Likwid</t>
-  </si>
-  <si>
-    <t>from   Raffin, Guillaume, and Denis Trystram. 2024. ‘Dissecting the Software-Based Measurement of CPU Energy Consumption: A Comparative Analysis’. arXiv:2401.15985. Preprint, arXiv, July 19. https://doi.org/10.48550/arXiv.2401.15985.
-J. Treibig, G. Hager, and G. Wellein. “LIKWID: a lightweight performance-oriented tool suite for x86 multicore environments”. In: Proceedings of PSTI2010, the First International Workshop on Parallel Software Tools and Tool Infrastructures. San Diego CA, 2010.</t>
-  </si>
-  <si>
-    <t>1Hz (Max 28Hz If modified as in (Raffin and Trystram 2024))</t>
-  </si>
-  <si>
-    <t>~Monitoring Cycle of 1s mentioned in (Noureddine et al. 2012)</t>
-  </si>
-  <si>
-    <t>Model-based (TDP)</t>
-  </si>
-  <si>
-    <t>Reported in (Noureddine et al. 2012; (Noureddine et al. 2015))</t>
-  </si>
-  <si>
-    <t>Two methods available: 
-1) Statistical Sampling of Call Stack --&gt; No Code Modification
-2) Source Code Instrumentation (i.e. time markers around functions)</t>
-  </si>
-  <si>
-    <t>yes (Java Applications)</t>
+    <t>IgProf (Energy module)</t>
+  </si>
+  <si>
+    <t>Function Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~5ms sampling interval in (Khan et al. 2015) </t>
+  </si>
+  <si>
+    <t>Attribution 
+Mechanism</t>
+  </si>
+  <si>
+    <t>Container Isolation : Accesses cgroups to learn about how resources are shared.</t>
+  </si>
+  <si>
+    <t>Khan, Kashif, Filip Nybäck, Zhonghong Ou, et al. 2015. Energy Profiling Using IgProf. In Proceedings - 2015 IEEE/ACM 15th International Symposium on Cluster, Cloud, and Grid Computing, CCGrid 2015. https://doi.org/10.1109/CCGrid.2015.118.
+G. Eulisse, L. Tuura: IgProf profiling tool, Proc. Computing In High Energy And Nuclear Physics (CHEP 2004), Interlaken, Switzerland, 2004</t>
+  </si>
+  <si>
+    <t>1) Allocate all RAPL system energy to process it is attached to
+2) Statistical Sampling (stack trace) to allocate energy to functions</t>
+  </si>
+  <si>
+    <t>1) Uses OS provided per-process (PID)resources utilisation to allocate energy to process (JVM)
+2a)A version with statistical sampling to allocate energy to methods/classes
+2b) A version with automatic bytecode instrumentation to attribute energy to methods/classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not modeled </t>
+  </si>
+  <si>
+    <t>trained model for system-level estimations in virtualised
+contex</t>
+  </si>
+  <si>
+    <t>✗ (RAPL throush powercap)</t>
+  </si>
+  <si>
+    <t>Qualitatively Reported in (Khan et al. 2015)</t>
+  </si>
+  <si>
+    <t>Not reported for Energy module</t>
+  </si>
+  <si>
+    <t>Runs as an attached library to the profiled process</t>
+  </si>
+  <si>
+    <t>Limited to not existing for the energy module
+(https://igprof.org/index.html)</t>
+  </si>
+  <si>
+    <t>✗(specific models)</t>
+  </si>
+  <si>
+    <t>✗(CPU energy on specific models)</t>
+  </si>
+  <si>
+    <t>✗ (RAPL throush PAPI)</t>
+  </si>
+  <si>
+    <t>Command line tool, export to csv</t>
+  </si>
+  <si>
+    <t>Joular Core</t>
+  </si>
+  <si>
+    <t>Support for VM "exposing System-level metrics in a shared file from host to VM"</t>
+  </si>
+  <si>
+    <t>Yes if provided by host</t>
+  </si>
+  <si>
+    <t>Not maintained since 2024</t>
+  </si>
+  <si>
+    <t>For Rasberry Pi</t>
+  </si>
+  <si>
+    <t>Application Level (All its PIDs)
+Process level (PID)</t>
+  </si>
+  <si>
+    <t>PowerJoular/JoularJX</t>
+  </si>
+  <si>
+    <t>`PowerJoular/JoularJX</t>
+  </si>
+  <si>
+    <t>JoularJX</t>
+  </si>
+  <si>
+    <t>Mostly statistical sampling --&gt; no code modification</t>
+  </si>
+  <si>
+    <t>✗(NVIDIA SMI) (computers and servers</t>
+  </si>
+  <si>
+    <t>PowerJoular is aimed to software developers, system administrators and to automated tools, with a goal to help these users understand the power consumption of their devices and software (Noureddine [2021] 2022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">btw 0.3% and 3.83% on RaspberryPie (Noureddine [2021] 2022)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~10ms
+</t>
+  </si>
+  <si>
+    <t>~1s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Allocation through Processes CPU utilization
+</t>
+  </si>
+  <si>
+    <t>1) Allocation through CPU utilization for Java Threads (1s)
+2) Statistical sampling of thread stack trace(10ms)</t>
+  </si>
+  <si>
+    <t>PowerJoular monitors the power consumption of CPU and GPU for PCs, servers and single-board computers (such as Raspberry Pi).
+JoularJX uses the power data provided by PowerJoular to monitor the power consumption of methods and source code in Java applications.
+These tools extend the strategies used for former PowerAPI/eJalen : runtime estimation are now possible</t>
+  </si>
+  <si>
+    <t>Support for Container "exposing System-level metrics in a shared file from host to VM"</t>
+  </si>
+  <si>
+    <t>Active (Last Commit in 2026)</t>
+  </si>
+  <si>
+    <t>Not reported but supposed to be low (1s sampling rate + written in Ada (low carbon language(Noureddine [2021] 2022)))</t>
+  </si>
+  <si>
+    <t>Not reported</t>
+  </si>
+  <si>
+    <t>no:  statistical sampling</t>
+  </si>
+  <si>
+    <t>Forward Snawballing</t>
+  </si>
+  <si>
+    <t>(Noureddine [2021] 2022)</t>
+  </si>
+  <si>
+    <t>Concice documentation : https://joular.github.io/powerjoular/overview.html</t>
+  </si>
+  <si>
+    <t>Designed for software Developers</t>
+  </si>
+  <si>
+    <t>Power Core is aimed to software developers, system administrators and to automated tools, with a goal to help these users understand the power consumption of their devices and software (Noureddine [2021] 2022)</t>
+  </si>
+  <si>
+    <t>Extension of PowerJoular to MacOs and Windows in a cross-platform implementation written in Rust.
+Joular Core is designed to be embedded in larger workflows. It exposes power data through multiple channels — terminal, CSV files, a shared-memory ring buffer, and an HTTP/WebSocket API — so it can feed into whatever downstream system you are working with. Also add a GUI for live monitoring</t>
+  </si>
+  <si>
+    <t>✗ (RAPL (linux/windows) or powerMetrics (Mac))</t>
+  </si>
+  <si>
+    <t>polynomial regression For Rasberry Pi</t>
+  </si>
+  <si>
+    <t>Baseline modeled and 
+substracted before allocation</t>
+  </si>
+  <si>
+    <t>Command line tool or Gui</t>
+  </si>
+  <si>
+    <t>MacSilicon</t>
+  </si>
+  <si>
+    <t>no reported</t>
+  </si>
+  <si>
+    <t>Active (Last Commit 2026)</t>
+  </si>
+  <si>
+    <t>Concice documentation : https://joular.github.io/joularcore/</t>
+  </si>
+  <si>
+    <t>Mobile but no attribution</t>
+  </si>
+  <si>
+    <t>e-Surgeon
+(PowerAPI+eJalen)</t>
+  </si>
+  <si>
+    <t>Method-Level</t>
+  </si>
+  <si>
+    <t>~ms</t>
+  </si>
+  <si>
+    <t>OS signals + power profiles</t>
+  </si>
+  <si>
+    <t>Time-based allocation (knows exactly entry/exit events of method)</t>
+  </si>
+  <si>
+    <t>Mean relative error: ~1% overall</t>
+  </si>
+  <si>
+    <t>Needs to run app in debug mode to access method traces</t>
   </si>
 </sst>
 </file>
@@ -774,7 +995,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -849,12 +1070,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -875,12 +1090,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1014,7 +1223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1111,13 +1320,10 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1129,9 +1335,6 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1153,11 +1356,56 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1216,10 +1464,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1228,53 +1476,47 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1844,7 +2086,7 @@
     <col min="2" max="2" width="8.5" style="11" customWidth="1"/>
     <col min="3" max="3" width="28" style="11" customWidth="1"/>
     <col min="4" max="4" width="219.33203125" style="18" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" style="11" customWidth="1"/>
     <col min="6" max="6" width="28" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.1640625" style="11" bestFit="1" customWidth="1"/>
@@ -1889,7 +2131,7 @@
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="44" t="s">
         <v>51</v>
       </c>
       <c r="E3" s="8">
@@ -1911,7 +2153,7 @@
         <v>35</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="80" x14ac:dyDescent="0.2">
@@ -1919,7 +2161,7 @@
       <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="44" t="s">
         <v>52</v>
       </c>
       <c r="E4" s="6">
@@ -1947,16 +2189,16 @@
     <row r="5" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B5"/>
       <c r="C5" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="44" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="6">
         <v>2012</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>53</v>
@@ -1971,7 +2213,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="48" x14ac:dyDescent="0.2">
@@ -1979,29 +2221,29 @@
       <c r="C6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="47" t="s">
-        <v>94</v>
+      <c r="D6" s="45" t="s">
+        <v>93</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>63</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="80" x14ac:dyDescent="0.2">
@@ -2009,20 +2251,20 @@
       <c r="C7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="44" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="8">
         <v>2020</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>30</v>
@@ -2031,52 +2273,52 @@
         <v>35</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B8"/>
       <c r="C8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="44" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="6">
         <v>2017</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="272" x14ac:dyDescent="0.2">
       <c r="B9"/>
       <c r="C9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="46" t="s">
         <v>104</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>103</v>
       </c>
       <c r="E9" s="6">
         <v>2025</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>53</v>
@@ -2085,13 +2327,13 @@
         <v>35</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="272" x14ac:dyDescent="0.2">
@@ -2099,20 +2341,20 @@
       <c r="C10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>181</v>
+      <c r="D10" s="47" t="s">
+        <v>178</v>
       </c>
       <c r="E10" s="6">
         <v>2015</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>30</v>
@@ -2121,28 +2363,28 @@
         <v>35</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="335" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="380" x14ac:dyDescent="0.2">
       <c r="B11"/>
       <c r="C11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="48" t="s">
-        <v>180</v>
+      <c r="D11" s="46" t="s">
+        <v>201</v>
       </c>
       <c r="E11" s="6">
         <v>2015</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>30</v>
@@ -2151,26 +2393,28 @@
         <v>35</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="32" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="80" x14ac:dyDescent="0.2">
       <c r="B12"/>
       <c r="C12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>182</v>
+        <v>221</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>179</v>
       </c>
       <c r="E12" s="6">
         <v>2021</v>
       </c>
-      <c r="F12" s="17"/>
+      <c r="F12" s="17" t="s">
+        <v>193</v>
+      </c>
       <c r="G12" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>30</v>
@@ -2178,41 +2422,82 @@
       <c r="J12" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="14"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="64" x14ac:dyDescent="0.2">
       <c r="B13"/>
-      <c r="D13" s="48"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C13" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="46"/>
+      <c r="E13" s="11">
+        <v>2026</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="H13" t="s">
+        <v>239</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B14"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="48"/>
+      <c r="C14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="46"/>
       <c r="E14" s="10"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="15"/>
+      <c r="G14" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>172</v>
+      </c>
       <c r="I14" s="7"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="48"/>
+      <c r="C15" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="46"/>
       <c r="E15" s="10"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="15"/>
+      <c r="G15" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>35</v>
+      </c>
       <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="48"/>
+      <c r="D16" s="46"/>
       <c r="E16" s="10"/>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
@@ -2224,7 +2509,7 @@
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="48"/>
+      <c r="D17" s="46"/>
       <c r="E17" s="10"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
@@ -2235,7 +2520,7 @@
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="48"/>
+      <c r="D18" s="46"/>
       <c r="E18" s="10"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
@@ -2246,7 +2531,7 @@
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="48"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="10"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
@@ -2257,7 +2542,7 @@
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="48"/>
+      <c r="D20" s="46"/>
       <c r="E20" s="10"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
@@ -2268,8 +2553,8 @@
     <row r="21" spans="2:11" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="48" t="s">
-        <v>102</v>
+      <c r="D21" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="18"/>
@@ -2281,7 +2566,7 @@
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="48"/>
+      <c r="D22" s="46"/>
       <c r="E22" s="10"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
@@ -2348,7 +2633,7 @@
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="10"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="48"/>
+      <c r="D29" s="46"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
       <c r="H29" s="15"/>
@@ -2358,356 +2643,359 @@
       <c r="C30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="48" t="s">
-        <v>168</v>
+      <c r="D30" s="46" t="s">
+        <v>167</v>
       </c>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
     </row>
     <row r="31" spans="2:11" ht="32" x14ac:dyDescent="0.2">
       <c r="B31" s="10"/>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="48" t="s">
-        <v>168</v>
+      <c r="D31" s="97" t="s">
+        <v>167</v>
       </c>
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="10"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="48"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="101"/>
       <c r="G32" s="18"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="10"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="48"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="101"/>
       <c r="G33" s="18"/>
     </row>
     <row r="34" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="B34" s="10"/>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="48" t="s">
-        <v>168</v>
+      <c r="D34" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="D35" s="48" t="s">
-        <v>168</v>
+      <c r="D35" s="46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="D36" s="48" t="s">
-        <v>168</v>
+      <c r="D36" s="46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="48" t="s">
-        <v>168</v>
+      <c r="D37" s="46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="48" t="s">
-        <v>168</v>
+      <c r="D38" s="46" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C39" s="6"/>
-      <c r="D39" s="48"/>
+      <c r="D39" s="46"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D40" s="48"/>
+      <c r="D40" s="46"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D41" s="48"/>
+      <c r="D41" s="46"/>
     </row>
     <row r="42" spans="2:7" ht="32" x14ac:dyDescent="0.2">
       <c r="C42" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="48" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D43" s="48"/>
+      <c r="D43" s="46"/>
     </row>
     <row r="44" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C44" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="46" t="s">
         <v>162</v>
-      </c>
-      <c r="D44" s="48" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C45" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D45" s="48" t="s">
         <v>163</v>
       </c>
+      <c r="D45" s="46" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D46" s="48"/>
+      <c r="D46" s="46"/>
     </row>
     <row r="47" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C47" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="D47" s="48" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="D47" s="46" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C48" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D48" s="48" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+      <c r="D48" s="46" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="3:4" ht="16" x14ac:dyDescent="0.2">
       <c r="C49" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="D49" s="48" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="D49" s="46" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D50" s="48"/>
+      <c r="D50" s="46"/>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D51" s="48"/>
+      <c r="D51" s="46"/>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D52" s="48"/>
+      <c r="D52" s="46"/>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D53" s="48"/>
+      <c r="D53" s="46"/>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="D54" s="48"/>
+        <v>124</v>
+      </c>
+      <c r="D54" s="46"/>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D55" s="48"/>
+      <c r="D55" s="46"/>
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D56" s="48"/>
+      <c r="D56" s="46"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D57" s="48"/>
+      <c r="D57" s="46"/>
     </row>
     <row r="58" spans="3:4" ht="48" x14ac:dyDescent="0.2">
       <c r="C58" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D58" s="48" t="s">
-        <v>184</v>
+        <v>180</v>
+      </c>
+      <c r="D58" s="46" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="48"/>
+      <c r="D59" s="46"/>
     </row>
     <row r="60" spans="3:4" ht="32" x14ac:dyDescent="0.2">
       <c r="C60" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>185</v>
+        <v>125</v>
+      </c>
+      <c r="D60" s="46" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D61" s="48"/>
+      <c r="D61" s="46"/>
     </row>
     <row r="62" spans="3:4" ht="32" x14ac:dyDescent="0.2">
       <c r="C62" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="48" t="s">
-        <v>187</v>
+        <v>183</v>
+      </c>
+      <c r="D62" s="46" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="3:4" ht="32" x14ac:dyDescent="0.2">
       <c r="C63" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D63" s="48" t="s">
-        <v>189</v>
+        <v>185</v>
+      </c>
+      <c r="D63" s="46" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="D64" s="48"/>
+      <c r="D64" s="46"/>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D65" s="48"/>
+      <c r="D65" s="46"/>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D66" s="48"/>
+      <c r="D66" s="46"/>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D67" s="48"/>
+      <c r="D67" s="46"/>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D68" s="48"/>
+      <c r="D68" s="46"/>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D69" s="48"/>
+      <c r="D69" s="46"/>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D70" s="48"/>
+      <c r="D70" s="46"/>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D71" s="48"/>
+      <c r="D71" s="46"/>
     </row>
     <row r="72" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D72" s="48"/>
+      <c r="D72" s="46"/>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="48"/>
+      <c r="D73" s="46"/>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D74" s="48"/>
+      <c r="D74" s="46"/>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D75" s="48"/>
+      <c r="D75" s="46"/>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D76" s="48"/>
+      <c r="D76" s="46"/>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D77" s="48"/>
+      <c r="D77" s="46"/>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D78" s="48"/>
+      <c r="D78" s="46"/>
     </row>
     <row r="79" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D79" s="48"/>
+      <c r="D79" s="46"/>
     </row>
     <row r="80" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D80" s="48"/>
+      <c r="D80" s="46"/>
     </row>
     <row r="81" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D81" s="48"/>
+      <c r="D81" s="46"/>
     </row>
     <row r="82" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D82" s="48"/>
+      <c r="D82" s="46"/>
     </row>
     <row r="83" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D83" s="48"/>
+      <c r="D83" s="46"/>
     </row>
     <row r="84" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D84" s="48"/>
+      <c r="D84" s="46"/>
     </row>
     <row r="85" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D85" s="48"/>
+      <c r="D85" s="46"/>
     </row>
     <row r="86" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D86" s="48"/>
+      <c r="D86" s="46"/>
     </row>
     <row r="87" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D87" s="48"/>
+      <c r="D87" s="46"/>
     </row>
     <row r="88" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D88" s="48"/>
+      <c r="D88" s="46"/>
     </row>
     <row r="89" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D89" s="48"/>
+      <c r="D89" s="46"/>
     </row>
     <row r="90" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D90" s="48"/>
+      <c r="D90" s="46"/>
     </row>
     <row r="91" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D91" s="48"/>
+      <c r="D91" s="46"/>
     </row>
     <row r="92" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D92" s="48"/>
+      <c r="D92" s="46"/>
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D93" s="48"/>
+      <c r="D93" s="46"/>
     </row>
     <row r="94" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D94" s="48"/>
+      <c r="D94" s="46"/>
     </row>
     <row r="95" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D95" s="48"/>
+      <c r="D95" s="46"/>
     </row>
     <row r="96" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D96" s="48"/>
+      <c r="D96" s="46"/>
     </row>
     <row r="97" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D97" s="48"/>
+      <c r="D97" s="46"/>
     </row>
     <row r="98" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D98" s="48"/>
+      <c r="D98" s="46"/>
     </row>
     <row r="99" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D99" s="48"/>
+      <c r="D99" s="46"/>
     </row>
     <row r="100" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D100" s="48"/>
+      <c r="D100" s="46"/>
     </row>
     <row r="101" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D101" s="48"/>
+      <c r="D101" s="46"/>
     </row>
     <row r="102" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D102" s="48"/>
+      <c r="D102" s="46"/>
     </row>
     <row r="103" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D103" s="48"/>
+      <c r="D103" s="46"/>
     </row>
     <row r="104" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D104" s="48"/>
+      <c r="D104" s="46"/>
     </row>
     <row r="105" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D105" s="48"/>
+      <c r="D105" s="46"/>
     </row>
     <row r="106" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D106" s="48"/>
+      <c r="D106" s="46"/>
     </row>
     <row r="107" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D107" s="48"/>
+      <c r="D107" s="46"/>
     </row>
     <row r="108" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D108" s="48"/>
+      <c r="D108" s="46"/>
     </row>
     <row r="109" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D109" s="48"/>
+      <c r="D109" s="46"/>
     </row>
     <row r="110" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D110" s="48"/>
+      <c r="D110" s="46"/>
     </row>
     <row r="111" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D111" s="48"/>
+      <c r="D111" s="46"/>
     </row>
     <row r="112" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D112" s="48"/>
+      <c r="D112" s="46"/>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D113" s="48"/>
+      <c r="D113" s="46"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I3:I16">
@@ -2789,16 +3077,16 @@
         <v>55</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>30</v>
@@ -2818,16 +3106,16 @@
         <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>30</v>
@@ -2844,19 +3132,19 @@
         <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>30</v>
@@ -2870,7 +3158,7 @@
         <v>55</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>55</v>
@@ -2879,16 +3167,16 @@
         <v>55</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -2905,16 +3193,16 @@
         <v>55</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>30</v>
@@ -2922,13 +3210,13 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>55</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>55</v>
@@ -2937,25 +3225,25 @@
         <v>55</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>55</v>
@@ -2964,28 +3252,46 @@
         <v>55</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="30"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="B10" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="30"/>
@@ -3122,201 +3428,201 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:AP30"/>
+  <dimension ref="B2:AQ30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.1640625" customWidth="1"/>
+    <col min="12" max="12" width="5.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28" customWidth="1"/>
-    <col min="16" max="16" width="24.1640625" customWidth="1"/>
-    <col min="17" max="17" width="19.5" customWidth="1"/>
-    <col min="18" max="18" width="26.1640625" customWidth="1"/>
-    <col min="19" max="19" width="24.5" customWidth="1"/>
-    <col min="20" max="20" width="34.1640625" customWidth="1"/>
-    <col min="21" max="21" width="22" customWidth="1"/>
-    <col min="22" max="22" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="30.83203125" customWidth="1"/>
-    <col min="24" max="24" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.33203125" customWidth="1"/>
-    <col min="30" max="30" width="12.33203125" customWidth="1"/>
-    <col min="31" max="31" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="26" customWidth="1"/>
-    <col min="33" max="33" width="17.6640625" customWidth="1"/>
-    <col min="34" max="34" width="15" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="52" customWidth="1"/>
-    <col min="36" max="36" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.6640625" customWidth="1"/>
+    <col min="22" max="22" width="20.5" customWidth="1"/>
+    <col min="23" max="23" width="32.1640625" customWidth="1"/>
+    <col min="24" max="24" width="28.5" customWidth="1"/>
+    <col min="25" max="25" width="21.83203125" customWidth="1"/>
+    <col min="26" max="26" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="11" customWidth="1"/>
+    <col min="33" max="33" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="26.83203125" customWidth="1"/>
-    <col min="40" max="40" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="55.83203125" customWidth="1"/>
-    <col min="42" max="42" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="31" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="46.1640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:42" ht="24" x14ac:dyDescent="0.3">
-      <c r="B2" s="60" t="s">
+    <row r="2" spans="2:43" ht="24" x14ac:dyDescent="0.3">
+      <c r="B2" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="77" t="s">
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="54" t="s">
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="W2" s="55"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="57" t="s">
+      <c r="X2" s="68"/>
+      <c r="Y2" s="69"/>
+      <c r="Z2" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="58"/>
-      <c r="AC2" s="58"/>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="58"/>
-      <c r="AH2" s="58"/>
-      <c r="AI2" s="58"/>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="90" t="s">
+      <c r="AA2" s="71"/>
+      <c r="AB2" s="71"/>
+      <c r="AC2" s="71"/>
+      <c r="AD2" s="71"/>
+      <c r="AE2" s="71"/>
+      <c r="AF2" s="71"/>
+      <c r="AG2" s="71"/>
+      <c r="AH2" s="71"/>
+      <c r="AI2" s="71"/>
+      <c r="AJ2" s="71"/>
+      <c r="AK2" s="71"/>
+      <c r="AL2" s="72"/>
+      <c r="AM2" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="91"/>
-      <c r="AN2" s="91"/>
-      <c r="AO2" s="91"/>
-      <c r="AP2" s="92"/>
-    </row>
-    <row r="3" spans="2:42" ht="24" x14ac:dyDescent="0.2">
-      <c r="B3" s="60"/>
-      <c r="C3" s="62" t="s">
+      <c r="AN2" s="65"/>
+      <c r="AO2" s="65"/>
+      <c r="AP2" s="65"/>
+      <c r="AQ2" s="66"/>
+    </row>
+    <row r="3" spans="2:43" ht="24" x14ac:dyDescent="0.2">
+      <c r="B3" s="73"/>
+      <c r="C3" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65" t="s">
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="69" t="s">
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="71" t="s">
+      <c r="O3" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="P3" s="79" t="s">
+      <c r="P3" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="T3" s="75" t="s">
+      <c r="Q3" s="91"/>
+      <c r="R3" s="91"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="U3" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="U3" s="73" t="s">
+      <c r="V3" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="86" t="s">
+      <c r="W3" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="W3" s="88" t="s">
+      <c r="X3" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="X3" s="86" t="s">
+      <c r="Y3" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="Y3" s="84" t="s">
+      <c r="Z3" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="Z3" s="84"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="84"/>
-      <c r="AC3" s="85" t="s">
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="80" t="s">
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="AH3" s="82" t="s">
+      <c r="AI3" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="AI3" s="80" t="s">
+      <c r="AJ3" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="AJ3" s="82" t="s">
+      <c r="AK3" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="AK3" s="80" t="s">
+      <c r="AL3" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="AL3" s="50" t="s">
+      <c r="AM3" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="AM3" s="52" t="s">
+      <c r="AN3" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="AN3" s="50" t="s">
+      <c r="AO3" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="AO3" s="52" t="s">
-        <v>100</v>
-      </c>
-      <c r="AP3" s="50" t="s">
+      <c r="AP3" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ3" s="48" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:42" ht="61" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="61"/>
+    <row r="4" spans="2:43" ht="61" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="74"/>
       <c r="C4" s="32" t="s">
         <v>56</v>
       </c>
@@ -3327,102 +3633,105 @@
         <v>58</v>
       </c>
       <c r="F4" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>117</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>118</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>59</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J4" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="37" t="s">
-        <v>88</v>
-      </c>
       <c r="L4" s="37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M4" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="70"/>
-      <c r="O4" s="72"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="85"/>
       <c r="P4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="Q4" s="20" t="s">
+      <c r="R4" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="R4" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="S4" s="74"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="74"/>
+      <c r="S4" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="T4" s="87"/>
+      <c r="U4" s="89"/>
       <c r="V4" s="87"/>
-      <c r="W4" s="89"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="24" t="s">
-        <v>86</v>
-      </c>
+      <c r="W4" s="59"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="59"/>
       <c r="Z4" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4" s="24" t="s">
         <v>68</v>
-      </c>
-      <c r="AA4" s="24" t="s">
-        <v>85</v>
       </c>
       <c r="AB4" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="AC4" s="40" t="s">
+      <c r="AC4" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD4" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="AD4" s="40" t="s">
+      <c r="AE4" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="AE4" s="40" t="s">
+      <c r="AF4" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="AF4" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="AG4" s="81"/>
-      <c r="AH4" s="83"/>
-      <c r="AI4" s="81"/>
-      <c r="AJ4" s="83"/>
-      <c r="AK4" s="81"/>
-      <c r="AL4" s="51"/>
-      <c r="AM4" s="53"/>
-      <c r="AN4" s="51"/>
-      <c r="AO4" s="53"/>
-      <c r="AP4" s="51"/>
-    </row>
-    <row r="5" spans="2:42" s="36" customFormat="1" ht="145" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="41" t="s">
+      <c r="AG4" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="55"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="55"/>
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="63"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="63"/>
+      <c r="AQ4" s="49"/>
+    </row>
+    <row r="5" spans="2:43" s="36" customFormat="1" ht="161" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="40" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E5" s="34" t="s">
         <v>60</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I5" s="34" t="s">
         <v>60</v>
@@ -3440,236 +3749,244 @@
         <v>60</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P5" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="U5" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="V5" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="W5" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="Q5" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="R5" s="34" t="s">
+      <c r="X5" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y5" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z5" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA5" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB5" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC5" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD5" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE5" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF5" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG5" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH5" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI5" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ5" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="S5" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="T5" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="U5" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="V5" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="W5" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="X5" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y5" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="Z5" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA5" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB5" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC5" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD5" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="AE5" s="35"/>
-      <c r="AF5" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="AG5" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH5" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI5" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ5" s="35" t="s">
-        <v>108</v>
-      </c>
       <c r="AK5" s="35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AL5" s="35" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="AM5" s="35" t="s">
         <v>120</v>
       </c>
       <c r="AN5" s="35" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="AO5" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP5" s="34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="2:42" s="36" customFormat="1" ht="192" x14ac:dyDescent="0.2">
-      <c r="B6" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="AP5" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="AQ5" s="34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="2:43" s="36" customFormat="1" ht="208" x14ac:dyDescent="0.2">
+      <c r="B6" s="41" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>108</v>
+      <c r="F6" s="38" t="s">
+        <v>107</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J6" s="34" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O6" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q6" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="P6" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q6" s="34" t="s">
+      <c r="R6" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="T6" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="R6" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="U6" s="38"/>
-      <c r="V6" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="W6" s="38"/>
-      <c r="X6" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y6" s="35" t="s">
-        <v>123</v>
+      <c r="U6" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="V6" s="94"/>
+      <c r="W6" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="X6" s="94"/>
+      <c r="Y6" s="38" t="s">
+        <v>147</v>
       </c>
       <c r="Z6" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA6" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="AA6" s="35" t="s">
-        <v>108</v>
-      </c>
       <c r="AB6" s="35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AC6" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
+      </c>
+      <c r="AD6" s="35" t="s">
+        <v>121</v>
       </c>
       <c r="AE6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AF6" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG6" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="AH6" s="35" t="s">
-        <v>60</v>
+        <v>107</v>
+      </c>
+      <c r="AH6" s="34" t="s">
+        <v>150</v>
       </c>
       <c r="AI6" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="AJ6" s="34" t="s">
+      <c r="AJ6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK6" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL6" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="AK6" s="34" t="s">
+      <c r="AM6" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="AL6" s="34" t="s">
+      <c r="AN6" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AM6" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="AN6" s="35" t="s">
+      <c r="AO6" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AP6" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AQ6" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AO6" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="AP6" s="34" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="2:42" s="36" customFormat="1" ht="160" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="2:43" s="36" customFormat="1" ht="128" x14ac:dyDescent="0.2">
       <c r="B7" s="42" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F7" s="34" t="s">
         <v>60</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J7" s="34" t="s">
         <v>60</v>
@@ -3678,99 +3995,106 @@
         <v>60</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N7" s="34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O7" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="P7" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="S7" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="T7" s="94" t="s">
+        <v>204</v>
+      </c>
+      <c r="U7" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="V7" s="94"/>
+      <c r="W7" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="P7" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q7" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="S7" s="38"/>
-      <c r="T7" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="U7" s="38"/>
-      <c r="V7" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="35" t="s">
-        <v>60</v>
-      </c>
+      <c r="X7" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y7" s="34"/>
       <c r="Z7" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="AA7" s="34" t="s">
-        <v>108</v>
+      <c r="AA7" s="35" t="s">
+        <v>60</v>
       </c>
       <c r="AB7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AC7" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD7" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="AD7" s="34"/>
       <c r="AE7" s="34"/>
       <c r="AF7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG7" s="34" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="AH7" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AI7" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AJ7" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AK7" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AL7" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM7" s="34"/>
+        <v>113</v>
+      </c>
+      <c r="AM7" s="34" t="s">
+        <v>120</v>
+      </c>
       <c r="AN7" s="34"/>
       <c r="AO7" s="34"/>
       <c r="AP7" s="34"/>
-    </row>
-    <row r="8" spans="2:42" s="36" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="43" t="s">
+      <c r="AQ7" s="34"/>
+    </row>
+    <row r="8" spans="2:43" s="36" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+      <c r="B8" s="41" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H8" s="34"/>
       <c r="I8" s="34" t="s">
@@ -3780,1057 +4104,1440 @@
         <v>60</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="L8" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="L8" s="43" t="s">
         <v>60</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R8" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="S8" s="38"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="W8" s="34"/>
+        <v>127</v>
+      </c>
+      <c r="S8" s="34"/>
+      <c r="T8" s="94"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34" t="s">
+        <v>107</v>
+      </c>
       <c r="X8" s="34"/>
-      <c r="Y8" s="35" t="s">
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB8" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC8" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE8" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF8" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG8" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH8" s="34" t="s">
         <v>157</v>
-      </c>
-      <c r="Z8" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA8" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC8" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF8" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG8" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="AH8" s="35" t="s">
-        <v>60</v>
       </c>
       <c r="AI8" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="AJ8" s="34"/>
-      <c r="AK8" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL8" s="34"/>
+      <c r="AJ8" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK8" s="34"/>
+      <c r="AL8" s="34" t="s">
+        <v>158</v>
+      </c>
       <c r="AM8" s="34"/>
       <c r="AN8" s="34"/>
       <c r="AO8" s="34"/>
       <c r="AP8" s="34"/>
-    </row>
-    <row r="9" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
+      <c r="AQ8" s="34"/>
+    </row>
+    <row r="9" spans="2:43" s="36" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="O9" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="S9" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="U9" s="34" t="s">
+        <v>207</v>
+      </c>
       <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="19"/>
-    </row>
-    <row r="10" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
+      <c r="W9" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y9" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z9" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA9" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC9" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD9" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL9" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM9" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN9" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="AO9" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP9" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ9" s="19"/>
+    </row>
+    <row r="10" spans="2:43" s="36" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="B10" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="U10" s="34" t="s">
+        <v>227</v>
+      </c>
       <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="19"/>
-      <c r="AG10" s="19"/>
-      <c r="AH10" s="19"/>
-      <c r="AI10" s="19"/>
-      <c r="AJ10" s="19"/>
-      <c r="AK10" s="19"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="19"/>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
-      <c r="AP10" s="19"/>
-    </row>
-    <row r="11" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
+      <c r="W10" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="X10" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y10" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z10" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA10" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB10" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC10" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD10" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE10" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF10" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG10" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH10" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="AI10" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="AJ10" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK10" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL10" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM10" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN10" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="AO10" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP10" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="AQ10" s="34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="2:43" s="36" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+      <c r="B11" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="O11" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q11" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>204</v>
+      </c>
       <c r="U11" s="19"/>
       <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="19"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="19"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
+      <c r="W11" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="X11" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y11" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z11" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA11" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC11" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD11" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE11" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF11" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG11" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH11" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI11" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ11" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK11" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL11" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM11" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN11" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="AO11" s="34" t="s">
+        <v>240</v>
+      </c>
       <c r="AP11" s="19"/>
-    </row>
-    <row r="12" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
+      <c r="AQ11" s="34" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="2:43" s="36" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="B12" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q12" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="S12" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>236</v>
+      </c>
       <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="19"/>
-      <c r="AG12" s="19"/>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="19"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="19"/>
-      <c r="AN12" s="19"/>
-      <c r="AO12" s="19"/>
+      <c r="W12" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="X12" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z12" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA12" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC12" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD12" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE12" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF12" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="AG12" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH12" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="AI12" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL12" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="AO12" s="34" t="s">
+        <v>251</v>
+      </c>
       <c r="AP12" s="19"/>
-    </row>
-    <row r="13" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="19"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="19"/>
-    </row>
-    <row r="14" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="19"/>
-      <c r="AG14" s="19"/>
-      <c r="AH14" s="19"/>
-      <c r="AI14" s="19"/>
-      <c r="AJ14" s="19"/>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="19"/>
-      <c r="AN14" s="19"/>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="19"/>
-    </row>
-    <row r="15" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="19"/>
-      <c r="AG15" s="19"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="19"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="19"/>
-      <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
-      <c r="AP15" s="19"/>
-    </row>
-    <row r="16" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="19"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="19"/>
-      <c r="AG16" s="19"/>
-      <c r="AH16" s="19"/>
-      <c r="AI16" s="19"/>
-      <c r="AJ16" s="19"/>
-      <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="19"/>
-      <c r="AN16" s="19"/>
-      <c r="AO16" s="19"/>
-      <c r="AP16" s="19"/>
-    </row>
-    <row r="17" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="19"/>
-      <c r="AH17" s="19"/>
-      <c r="AI17" s="19"/>
-      <c r="AJ17" s="19"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="19"/>
-      <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
-      <c r="AP17" s="19"/>
-    </row>
-    <row r="18" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="19"/>
-      <c r="AG18" s="19"/>
-      <c r="AH18" s="19"/>
-      <c r="AI18" s="19"/>
-      <c r="AJ18" s="19"/>
-      <c r="AK18" s="19"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="19"/>
-      <c r="AN18" s="19"/>
-      <c r="AO18" s="19"/>
-      <c r="AP18" s="19"/>
-    </row>
-    <row r="19" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
-      <c r="AE19" s="19"/>
-      <c r="AF19" s="19"/>
-      <c r="AG19" s="19"/>
-      <c r="AH19" s="19"/>
-      <c r="AI19" s="19"/>
-      <c r="AJ19" s="19"/>
-      <c r="AK19" s="19"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="19"/>
-      <c r="AN19" s="19"/>
-      <c r="AO19" s="19"/>
-      <c r="AP19" s="19"/>
-    </row>
-    <row r="20" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="19"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="19"/>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="19"/>
-      <c r="AG20" s="19"/>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="19"/>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="19"/>
-    </row>
-    <row r="21" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="19"/>
-      <c r="AG21" s="19"/>
-      <c r="AH21" s="19"/>
-      <c r="AI21" s="19"/>
-      <c r="AJ21" s="19"/>
-      <c r="AK21" s="19"/>
-      <c r="AL21" s="19"/>
-      <c r="AM21" s="19"/>
-      <c r="AN21" s="19"/>
-      <c r="AO21" s="19"/>
-      <c r="AP21" s="19"/>
-    </row>
-    <row r="22" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="19"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="19"/>
-      <c r="AG22" s="19"/>
-      <c r="AH22" s="19"/>
-      <c r="AI22" s="19"/>
-      <c r="AJ22" s="19"/>
-      <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="19"/>
-      <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="19"/>
-    </row>
-    <row r="23" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="19"/>
-      <c r="AG23" s="19"/>
-      <c r="AH23" s="19"/>
-      <c r="AI23" s="19"/>
-      <c r="AJ23" s="19"/>
-      <c r="AK23" s="19"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="19"/>
-      <c r="AN23" s="19"/>
-      <c r="AO23" s="19"/>
-      <c r="AP23" s="19"/>
-    </row>
-    <row r="24" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="19"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="19"/>
-      <c r="AG24" s="19"/>
-      <c r="AH24" s="19"/>
-      <c r="AI24" s="19"/>
-      <c r="AJ24" s="19"/>
-      <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="19"/>
-      <c r="AN24" s="19"/>
-      <c r="AO24" s="19"/>
-      <c r="AP24" s="19"/>
-    </row>
-    <row r="25" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="19"/>
-      <c r="AG25" s="19"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
-      <c r="AJ25" s="19"/>
-      <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
-      <c r="AM25" s="19"/>
-      <c r="AN25" s="19"/>
-      <c r="AO25" s="19"/>
-      <c r="AP25" s="19"/>
-    </row>
-    <row r="26" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="19"/>
-      <c r="Z26" s="19"/>
-      <c r="AA26" s="19"/>
-      <c r="AB26" s="19"/>
-      <c r="AC26" s="19"/>
-      <c r="AD26" s="19"/>
-      <c r="AE26" s="19"/>
-      <c r="AF26" s="19"/>
-      <c r="AG26" s="19"/>
-      <c r="AH26" s="19"/>
-      <c r="AI26" s="19"/>
-      <c r="AJ26" s="19"/>
-      <c r="AK26" s="19"/>
-      <c r="AL26" s="19"/>
-      <c r="AM26" s="19"/>
-      <c r="AN26" s="19"/>
-      <c r="AO26" s="19"/>
-      <c r="AP26" s="19"/>
-    </row>
-    <row r="27" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="19"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="19"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="19"/>
-      <c r="AC27" s="19"/>
-      <c r="AD27" s="19"/>
-      <c r="AE27" s="19"/>
-      <c r="AF27" s="19"/>
-      <c r="AG27" s="19"/>
-      <c r="AH27" s="19"/>
-      <c r="AI27" s="19"/>
-      <c r="AJ27" s="19"/>
-      <c r="AK27" s="19"/>
-      <c r="AL27" s="19"/>
-      <c r="AM27" s="19"/>
-      <c r="AN27" s="19"/>
-      <c r="AO27" s="19"/>
-      <c r="AP27" s="19"/>
-    </row>
-    <row r="28" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="19"/>
-      <c r="AB28" s="19"/>
-      <c r="AC28" s="19"/>
-      <c r="AD28" s="19"/>
-      <c r="AE28" s="19"/>
-      <c r="AF28" s="19"/>
-      <c r="AG28" s="19"/>
-      <c r="AH28" s="19"/>
-      <c r="AI28" s="19"/>
-      <c r="AJ28" s="19"/>
-      <c r="AK28" s="19"/>
-      <c r="AL28" s="19"/>
-      <c r="AM28" s="19"/>
-      <c r="AN28" s="19"/>
-      <c r="AO28" s="19"/>
-      <c r="AP28" s="19"/>
-    </row>
-    <row r="29" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="19"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="19"/>
-      <c r="Z29" s="19"/>
-      <c r="AA29" s="19"/>
-      <c r="AB29" s="19"/>
-      <c r="AC29" s="19"/>
-      <c r="AD29" s="19"/>
-      <c r="AE29" s="19"/>
-      <c r="AF29" s="19"/>
-      <c r="AG29" s="19"/>
-      <c r="AH29" s="19"/>
-      <c r="AI29" s="19"/>
-      <c r="AJ29" s="19"/>
-      <c r="AK29" s="19"/>
-      <c r="AL29" s="19"/>
-      <c r="AM29" s="19"/>
-      <c r="AN29" s="19"/>
-      <c r="AO29" s="19"/>
-      <c r="AP29" s="19"/>
-    </row>
-    <row r="30" spans="2:42" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="19"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="19"/>
-      <c r="Z30" s="19"/>
-      <c r="AA30" s="19"/>
-      <c r="AB30" s="19"/>
-      <c r="AC30" s="19"/>
-      <c r="AD30" s="19"/>
-      <c r="AE30" s="19"/>
-      <c r="AF30" s="19"/>
-      <c r="AG30" s="19"/>
-      <c r="AH30" s="19"/>
-      <c r="AI30" s="19"/>
-      <c r="AJ30" s="19"/>
-      <c r="AK30" s="19"/>
-      <c r="AL30" s="19"/>
-      <c r="AM30" s="19"/>
-      <c r="AN30" s="19"/>
-      <c r="AO30" s="19"/>
-      <c r="AP30" s="19"/>
+      <c r="AQ12" s="34" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="2:43" s="38" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="B13" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="O13" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q13" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="T13" s="34"/>
+      <c r="U13" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="V13" s="34"/>
+      <c r="W13" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB13" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="34"/>
+      <c r="AJ13" s="34"/>
+      <c r="AK13" s="34"/>
+      <c r="AL13" s="34"/>
+      <c r="AM13" s="34"/>
+      <c r="AN13" s="34"/>
+      <c r="AO13" s="34"/>
+      <c r="AP13" s="34"/>
+      <c r="AQ13" s="34"/>
+    </row>
+    <row r="14" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="34"/>
+      <c r="V14" s="34"/>
+      <c r="W14" s="34"/>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="34"/>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="34"/>
+      <c r="AC14" s="34"/>
+      <c r="AD14" s="34"/>
+      <c r="AE14" s="34"/>
+      <c r="AF14" s="34"/>
+      <c r="AG14" s="34"/>
+      <c r="AH14" s="34"/>
+      <c r="AI14" s="34"/>
+      <c r="AJ14" s="34"/>
+      <c r="AK14" s="34"/>
+      <c r="AL14" s="34"/>
+      <c r="AM14" s="34"/>
+      <c r="AN14" s="34"/>
+      <c r="AO14" s="34"/>
+      <c r="AP14" s="34"/>
+      <c r="AQ14" s="34"/>
+    </row>
+    <row r="15" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="34"/>
+      <c r="W15" s="34"/>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="34"/>
+      <c r="Z15" s="34"/>
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="34"/>
+      <c r="AC15" s="34"/>
+      <c r="AD15" s="34"/>
+      <c r="AE15" s="34"/>
+      <c r="AF15" s="34"/>
+      <c r="AG15" s="34"/>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="34"/>
+      <c r="AJ15" s="34"/>
+      <c r="AK15" s="34"/>
+      <c r="AL15" s="34"/>
+      <c r="AM15" s="34"/>
+      <c r="AN15" s="34"/>
+      <c r="AO15" s="34"/>
+      <c r="AP15" s="34"/>
+      <c r="AQ15" s="34"/>
+    </row>
+    <row r="16" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="34"/>
+      <c r="AC16" s="34"/>
+      <c r="AD16" s="34"/>
+      <c r="AE16" s="34"/>
+      <c r="AF16" s="34"/>
+      <c r="AG16" s="34"/>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="34"/>
+      <c r="AJ16" s="34"/>
+      <c r="AK16" s="34"/>
+      <c r="AL16" s="34"/>
+      <c r="AM16" s="34"/>
+      <c r="AN16" s="34"/>
+      <c r="AO16" s="34"/>
+      <c r="AP16" s="34"/>
+      <c r="AQ16" s="34"/>
+    </row>
+    <row r="17" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="34"/>
+      <c r="W17" s="34"/>
+      <c r="X17" s="34"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="34"/>
+      <c r="AE17" s="34"/>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="34"/>
+      <c r="AJ17" s="34"/>
+      <c r="AK17" s="34"/>
+      <c r="AL17" s="34"/>
+      <c r="AM17" s="34"/>
+      <c r="AN17" s="34"/>
+      <c r="AO17" s="34"/>
+      <c r="AP17" s="34"/>
+      <c r="AQ17" s="34"/>
+    </row>
+    <row r="18" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="34"/>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="34"/>
+      <c r="AC18" s="34"/>
+      <c r="AD18" s="34"/>
+      <c r="AE18" s="34"/>
+      <c r="AF18" s="34"/>
+      <c r="AG18" s="34"/>
+      <c r="AH18" s="34"/>
+      <c r="AI18" s="34"/>
+      <c r="AJ18" s="34"/>
+      <c r="AK18" s="34"/>
+      <c r="AL18" s="34"/>
+      <c r="AM18" s="34"/>
+      <c r="AN18" s="34"/>
+      <c r="AO18" s="34"/>
+      <c r="AP18" s="34"/>
+      <c r="AQ18" s="34"/>
+    </row>
+    <row r="19" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="34"/>
+      <c r="W19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19" s="34"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="34"/>
+      <c r="AC19" s="34"/>
+      <c r="AD19" s="34"/>
+      <c r="AE19" s="34"/>
+      <c r="AF19" s="34"/>
+      <c r="AG19" s="34"/>
+      <c r="AH19" s="34"/>
+      <c r="AI19" s="34"/>
+      <c r="AJ19" s="34"/>
+      <c r="AK19" s="34"/>
+      <c r="AL19" s="34"/>
+      <c r="AM19" s="34"/>
+      <c r="AN19" s="34"/>
+      <c r="AO19" s="34"/>
+      <c r="AP19" s="34"/>
+      <c r="AQ19" s="34"/>
+    </row>
+    <row r="20" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="34"/>
+      <c r="AE20" s="34"/>
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="34"/>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="34"/>
+      <c r="AJ20" s="34"/>
+      <c r="AK20" s="34"/>
+      <c r="AL20" s="34"/>
+      <c r="AM20" s="34"/>
+      <c r="AN20" s="34"/>
+      <c r="AO20" s="34"/>
+      <c r="AP20" s="34"/>
+      <c r="AQ20" s="34"/>
+    </row>
+    <row r="21" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="34"/>
+      <c r="AA21" s="34"/>
+      <c r="AB21" s="34"/>
+      <c r="AC21" s="34"/>
+      <c r="AD21" s="34"/>
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="34"/>
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="34"/>
+      <c r="AJ21" s="34"/>
+      <c r="AK21" s="34"/>
+      <c r="AL21" s="34"/>
+      <c r="AM21" s="34"/>
+      <c r="AN21" s="34"/>
+      <c r="AO21" s="34"/>
+      <c r="AP21" s="34"/>
+      <c r="AQ21" s="34"/>
+    </row>
+    <row r="22" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="34"/>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="34"/>
+      <c r="AJ22" s="34"/>
+      <c r="AK22" s="34"/>
+      <c r="AL22" s="34"/>
+      <c r="AM22" s="34"/>
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="34"/>
+      <c r="AP22" s="34"/>
+      <c r="AQ22" s="34"/>
+    </row>
+    <row r="23" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23" s="34"/>
+      <c r="AA23" s="34"/>
+      <c r="AB23" s="34"/>
+      <c r="AC23" s="34"/>
+      <c r="AD23" s="34"/>
+      <c r="AE23" s="34"/>
+      <c r="AF23" s="34"/>
+      <c r="AG23" s="34"/>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="34"/>
+      <c r="AJ23" s="34"/>
+      <c r="AK23" s="34"/>
+      <c r="AL23" s="34"/>
+      <c r="AM23" s="34"/>
+      <c r="AN23" s="34"/>
+      <c r="AO23" s="34"/>
+      <c r="AP23" s="34"/>
+      <c r="AQ23" s="34"/>
+    </row>
+    <row r="24" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="34"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24" s="34"/>
+      <c r="AA24" s="34"/>
+      <c r="AB24" s="34"/>
+      <c r="AC24" s="34"/>
+      <c r="AD24" s="34"/>
+      <c r="AE24" s="34"/>
+      <c r="AF24" s="34"/>
+      <c r="AG24" s="34"/>
+      <c r="AH24" s="34"/>
+      <c r="AI24" s="34"/>
+      <c r="AJ24" s="34"/>
+      <c r="AK24" s="34"/>
+      <c r="AL24" s="34"/>
+      <c r="AM24" s="34"/>
+      <c r="AN24" s="34"/>
+      <c r="AO24" s="34"/>
+      <c r="AP24" s="34"/>
+      <c r="AQ24" s="34"/>
+    </row>
+    <row r="25" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="34"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="34"/>
+      <c r="AA25" s="34"/>
+      <c r="AB25" s="34"/>
+      <c r="AC25" s="34"/>
+      <c r="AD25" s="34"/>
+      <c r="AE25" s="34"/>
+      <c r="AF25" s="34"/>
+      <c r="AG25" s="34"/>
+      <c r="AH25" s="34"/>
+      <c r="AI25" s="34"/>
+      <c r="AJ25" s="34"/>
+      <c r="AK25" s="34"/>
+      <c r="AL25" s="34"/>
+      <c r="AM25" s="34"/>
+      <c r="AN25" s="34"/>
+      <c r="AO25" s="34"/>
+      <c r="AP25" s="34"/>
+      <c r="AQ25" s="34"/>
+    </row>
+    <row r="26" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="X26" s="34"/>
+      <c r="Y26" s="34"/>
+      <c r="Z26" s="34"/>
+      <c r="AA26" s="34"/>
+      <c r="AB26" s="34"/>
+      <c r="AC26" s="34"/>
+      <c r="AD26" s="34"/>
+      <c r="AE26" s="34"/>
+      <c r="AF26" s="34"/>
+      <c r="AG26" s="34"/>
+      <c r="AH26" s="34"/>
+      <c r="AI26" s="34"/>
+      <c r="AJ26" s="34"/>
+      <c r="AK26" s="34"/>
+      <c r="AL26" s="34"/>
+      <c r="AM26" s="34"/>
+      <c r="AN26" s="34"/>
+      <c r="AO26" s="34"/>
+      <c r="AP26" s="34"/>
+      <c r="AQ26" s="34"/>
+    </row>
+    <row r="27" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="34"/>
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="34"/>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="34"/>
+      <c r="AD27" s="34"/>
+      <c r="AE27" s="34"/>
+      <c r="AF27" s="34"/>
+      <c r="AG27" s="34"/>
+      <c r="AH27" s="34"/>
+      <c r="AI27" s="34"/>
+      <c r="AJ27" s="34"/>
+      <c r="AK27" s="34"/>
+      <c r="AL27" s="34"/>
+      <c r="AM27" s="34"/>
+      <c r="AN27" s="34"/>
+      <c r="AO27" s="34"/>
+      <c r="AP27" s="34"/>
+      <c r="AQ27" s="34"/>
+    </row>
+    <row r="28" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28" s="34"/>
+      <c r="AA28" s="34"/>
+      <c r="AB28" s="34"/>
+      <c r="AC28" s="34"/>
+      <c r="AD28" s="34"/>
+      <c r="AE28" s="34"/>
+      <c r="AF28" s="34"/>
+      <c r="AG28" s="34"/>
+      <c r="AH28" s="34"/>
+      <c r="AI28" s="34"/>
+      <c r="AJ28" s="34"/>
+      <c r="AK28" s="34"/>
+      <c r="AL28" s="34"/>
+      <c r="AM28" s="34"/>
+      <c r="AN28" s="34"/>
+      <c r="AO28" s="34"/>
+      <c r="AP28" s="34"/>
+      <c r="AQ28" s="34"/>
+    </row>
+    <row r="29" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29" s="34"/>
+      <c r="AA29" s="34"/>
+      <c r="AB29" s="34"/>
+      <c r="AC29" s="34"/>
+      <c r="AD29" s="34"/>
+      <c r="AE29" s="34"/>
+      <c r="AF29" s="34"/>
+      <c r="AG29" s="34"/>
+      <c r="AH29" s="34"/>
+      <c r="AI29" s="34"/>
+      <c r="AJ29" s="34"/>
+      <c r="AK29" s="34"/>
+      <c r="AL29" s="34"/>
+      <c r="AM29" s="34"/>
+      <c r="AN29" s="34"/>
+      <c r="AO29" s="34"/>
+      <c r="AP29" s="34"/>
+      <c r="AQ29" s="34"/>
+    </row>
+    <row r="30" spans="2:43" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="34"/>
+      <c r="AA30" s="34"/>
+      <c r="AB30" s="34"/>
+      <c r="AC30" s="34"/>
+      <c r="AD30" s="34"/>
+      <c r="AE30" s="34"/>
+      <c r="AF30" s="34"/>
+      <c r="AG30" s="34"/>
+      <c r="AH30" s="34"/>
+      <c r="AI30" s="34"/>
+      <c r="AJ30" s="34"/>
+      <c r="AK30" s="34"/>
+      <c r="AL30" s="34"/>
+      <c r="AM30" s="34"/>
+      <c r="AN30" s="34"/>
+      <c r="AO30" s="34"/>
+      <c r="AP30" s="34"/>
+      <c r="AQ30" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="AM3:AM4"/>
     <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="AH3:AH4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AJ3:AJ4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="Y3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AL2:AP2"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="Y2:AK2"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="J3:M3"/>
     <mergeCell ref="C2:O2"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
-    <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AL2"/>
+    <mergeCell ref="AM2:AQ2"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AH3:AH4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AJ3:AJ4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="AP3:AP4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
